--- a/Results2.xlsx
+++ b/Results2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A67077-982E-4FCD-9708-05E89B2FC6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B2F926-70EC-4A06-ADCC-E85D2FFE294C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2132F57B-8824-4764-BC02-18EC8AEFAB7F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>Name</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>Derda</t>
   </si>
   <si>
     <t>DULOIYI681</t>
@@ -388,6 +385,21 @@
   </si>
   <si>
     <t>Zorrillo</t>
+  </si>
+  <si>
+    <t>MaeTWF</t>
+  </si>
+  <si>
+    <t>Jahannm</t>
+  </si>
+  <si>
+    <t>Fury</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Ragefury</t>
   </si>
 </sst>
 </file>
@@ -965,22 +977,22 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1">
-        <v>3652</v>
+        <v>4716</v>
       </c>
       <c r="C2" s="1">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -989,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -1001,10 +1013,10 @@
         <v>1</v>
       </c>
       <c r="M2" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N2" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O2" s="1">
         <v>2</v>
@@ -1106,31 +1118,31 @@
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1">
-        <v>1712</v>
+        <v>3538</v>
       </c>
       <c r="C3" s="1">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -1139,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M3" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -1175,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="1">
         <v>0</v>
@@ -1187,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="AB3" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC3" s="1">
         <v>0</v>
@@ -1247,49 +1259,49 @@
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1">
-        <v>1504</v>
+        <v>2980</v>
       </c>
       <c r="C4" s="1">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>20</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
       <c r="O4" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P4" s="1">
         <v>0</v>
@@ -1316,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="1">
         <v>0</v>
@@ -1346,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
@@ -1388,94 +1400,94 @@
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B5" s="1">
-        <v>1460</v>
+        <v>2349</v>
       </c>
       <c r="C5" s="1">
+        <v>140</v>
+      </c>
+      <c r="D5" s="1">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>17</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>24</v>
+      </c>
+      <c r="N5" s="1">
+        <v>6</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
+        <v>30</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
         <v>4</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>13</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>0</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>0</v>
-      </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD5" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="1">
         <v>0</v>
@@ -1487,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -1529,19 +1541,19 @@
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B6" s="1">
-        <v>1435</v>
+        <v>1971</v>
       </c>
       <c r="C6" s="1">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1550,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1565,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
@@ -1613,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="1">
         <v>0</v>
@@ -1628,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
@@ -1670,22 +1682,22 @@
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1">
-        <v>1300</v>
+        <v>1930</v>
       </c>
       <c r="C7" s="1">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1694,64 +1706,64 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>6</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
         <v>5</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>5</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
         <v>4</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>8</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>6</v>
-      </c>
       <c r="Z7" s="1">
         <v>0</v>
       </c>
       <c r="AA7" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
@@ -1769,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -1811,22 +1823,22 @@
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1">
-        <v>1280</v>
+        <v>1892</v>
       </c>
       <c r="C8" s="1">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1835,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -1853,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -1889,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
@@ -1952,31 +1964,31 @@
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1">
-        <v>1091</v>
+        <v>1873</v>
       </c>
       <c r="C9" s="1">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1985,14 +1997,14 @@
         <v>0</v>
       </c>
       <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>9</v>
+      </c>
+      <c r="N9" s="1">
         <v>3</v>
       </c>
-      <c r="M9" s="1">
-        <v>20</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
       <c r="O9" s="1">
         <v>0</v>
       </c>
@@ -2018,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X9" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
@@ -2030,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="AA9" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
       </c>
       <c r="AC9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="1">
         <v>0</v>
@@ -2048,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="AG9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -2093,22 +2105,22 @@
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1">
-        <v>1080</v>
+        <v>1830</v>
       </c>
       <c r="C10" s="1">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2120,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -2132,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -2153,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V10" s="1">
         <v>0</v>
@@ -2165,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z10" s="1">
         <v>0</v>
@@ -2180,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE10" s="1">
         <v>0</v>
@@ -2234,106 +2246,106 @@
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
-        <v>838</v>
+        <v>1809</v>
       </c>
       <c r="C11" s="1">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1">
         <v>3</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2</v>
-      </c>
-      <c r="H11" s="1">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="1">
         <v>3</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>4</v>
-      </c>
-      <c r="N11" s="1">
-        <v>2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
-      </c>
-      <c r="W11" s="1">
-        <v>3</v>
-      </c>
-      <c r="X11" s="1">
-        <v>12</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>0</v>
       </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -2375,106 +2387,106 @@
     </row>
     <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1">
-        <v>726</v>
+        <v>1600</v>
       </c>
       <c r="C12" s="1">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>13</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1">
         <v>3</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-      <c r="U12" s="1">
-        <v>3</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>0</v>
       </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -2516,31 +2528,31 @@
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1">
-        <v>702</v>
+        <v>1498</v>
       </c>
       <c r="C13" s="1">
+        <v>65</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
         <v>14</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -2555,10 +2567,10 @@
         <v>4</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -2585,19 +2597,19 @@
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
       </c>
       <c r="AB13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="1">
         <v>0</v>
@@ -2657,19 +2669,19 @@
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B14" s="1">
-        <v>669</v>
+        <v>1440</v>
       </c>
       <c r="C14" s="1">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
         <v>6</v>
@@ -2681,55 +2693,55 @@
         <v>0</v>
       </c>
       <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>9</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>5</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
         <v>2</v>
-      </c>
-      <c r="J14" s="1">
-        <v>4</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>0</v>
       </c>
       <c r="Z14" s="1">
         <v>0</v>
@@ -2798,89 +2810,89 @@
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="B15" s="1">
-        <v>612</v>
+        <v>1430</v>
       </c>
       <c r="C15" s="1">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>4</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>8</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>8</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>11</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
       <c r="AC15" s="1">
         <v>0</v>
       </c>
@@ -2897,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2942,19 +2954,19 @@
         <v>87</v>
       </c>
       <c r="B16" s="1">
-        <v>591</v>
+        <v>1392</v>
       </c>
       <c r="C16" s="1">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -2969,62 +2981,62 @@
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="1">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1">
         <v>3</v>
       </c>
-      <c r="N16" s="1">
-        <v>2</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="1">
-        <v>1</v>
-      </c>
-      <c r="X16" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="1">
-        <v>0</v>
-      </c>
       <c r="AD16" s="1">
         <v>0</v>
       </c>
@@ -3035,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="AG16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -3080,22 +3092,22 @@
     </row>
     <row r="17" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B17" s="1">
-        <v>589</v>
+        <v>1310</v>
       </c>
       <c r="C17" s="1">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3104,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -3116,13 +3128,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -3140,13 +3152,13 @@
         <v>0</v>
       </c>
       <c r="U17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
       </c>
       <c r="W17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
@@ -3221,22 +3233,22 @@
     </row>
     <row r="18" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B18" s="1">
-        <v>550</v>
+        <v>1287</v>
       </c>
       <c r="C18" s="1">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -3245,62 +3257,62 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>13</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
         <v>3</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>3</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
-        <v>0</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
-      </c>
-      <c r="W18" s="1">
-        <v>0</v>
-      </c>
-      <c r="X18" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>0</v>
-      </c>
       <c r="AB18" s="1">
         <v>0</v>
       </c>
@@ -3320,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
@@ -3362,23 +3374,23 @@
     </row>
     <row r="19" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B19" s="1">
-        <v>547</v>
+        <v>1280</v>
       </c>
       <c r="C19" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="1">
-        <v>5</v>
-      </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
@@ -3389,22 +3401,22 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
         <v>6</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -3503,22 +3515,22 @@
     </row>
     <row r="20" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B20" s="1">
-        <v>533</v>
+        <v>1220</v>
       </c>
       <c r="C20" s="1">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -3530,16 +3542,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
@@ -3575,13 +3587,13 @@
         <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z20" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -3644,22 +3656,22 @@
     </row>
     <row r="21" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1">
-        <v>515</v>
+        <v>1174</v>
       </c>
       <c r="C21" s="1">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -3668,22 +3680,22 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
         <v>2</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>3</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -3713,22 +3725,22 @@
         <v>0</v>
       </c>
       <c r="X21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
       <c r="AB21" s="1">
         <v>0</v>
       </c>
       <c r="AC21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="1">
         <v>0</v>
@@ -3743,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3785,19 +3797,19 @@
     </row>
     <row r="22" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="B22" s="1">
-        <v>500</v>
+        <v>1139</v>
       </c>
       <c r="C22" s="1">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3809,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
@@ -3821,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N22" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -3845,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -3863,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3926,85 +3938,85 @@
     </row>
     <row r="23" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B23" s="1">
-        <v>500</v>
+        <v>1121</v>
       </c>
       <c r="C23" s="1">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1">
+        <v>8</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
       <c r="J23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>9</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
         <v>1</v>
       </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
       <c r="W23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -4067,68 +4079,68 @@
     </row>
     <row r="24" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1">
-        <v>496</v>
+        <v>1084</v>
       </c>
       <c r="C24" s="1">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
         <v>3</v>
       </c>
-      <c r="F24" s="1">
-        <v>17</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>0</v>
-      </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>0</v>
-      </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
-        <v>0</v>
-      </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
@@ -4136,20 +4148,20 @@
         <v>0</v>
       </c>
       <c r="X24" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
         <v>1</v>
       </c>
-      <c r="Y24" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>0</v>
-      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -4166,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
@@ -4208,22 +4220,22 @@
     </row>
     <row r="25" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1">
-        <v>493</v>
+        <v>910</v>
       </c>
       <c r="C25" s="1">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -4232,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
@@ -4244,44 +4256,44 @@
         <v>0</v>
       </c>
       <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>8</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1">
+        <v>2</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0</v>
-      </c>
-      <c r="V25" s="1">
-        <v>0</v>
-      </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>2</v>
-      </c>
       <c r="Z25" s="1">
         <v>0</v>
       </c>
@@ -4289,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4349,28 +4361,28 @@
     </row>
     <row r="26" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B26" s="1">
-        <v>443</v>
+        <v>910</v>
       </c>
       <c r="C26" s="1">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -4382,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
@@ -4415,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y26" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="1">
         <v>0</v>
@@ -4433,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -4490,22 +4502,22 @@
     </row>
     <row r="27" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B27" s="1">
-        <v>430</v>
+        <v>905</v>
       </c>
       <c r="C27" s="1">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -4523,46 +4535,46 @@
         <v>0</v>
       </c>
       <c r="L27" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
         <v>1</v>
       </c>
-      <c r="N27" s="1">
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="1">
         <v>2</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
-        <v>0</v>
-      </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>0</v>
       </c>
       <c r="Z27" s="1">
         <v>0</v>
@@ -4586,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="1">
         <v>3</v>
@@ -4631,22 +4643,22 @@
     </row>
     <row r="28" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B28" s="1">
-        <v>398</v>
+        <v>901</v>
       </c>
       <c r="C28" s="1">
+        <v>43</v>
+      </c>
+      <c r="D28" s="1">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
         <v>14</v>
       </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>4</v>
-      </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -4658,19 +4670,19 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -4697,13 +4709,13 @@
         <v>0</v>
       </c>
       <c r="W28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z28" s="1">
         <v>0</v>
@@ -4772,16 +4784,16 @@
     </row>
     <row r="29" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="B29" s="1">
-        <v>288</v>
+        <v>868</v>
       </c>
       <c r="C29" s="1">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -4805,16 +4817,16 @@
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N29" s="1">
         <v>0</v>
       </c>
       <c r="O29" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" s="1">
         <v>0</v>
@@ -4841,19 +4853,19 @@
         <v>0</v>
       </c>
       <c r="X29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" s="1">
         <v>0</v>
@@ -4913,22 +4925,22 @@
     </row>
     <row r="30" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="B30" s="1">
-        <v>271</v>
+        <v>867</v>
       </c>
       <c r="C30" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4937,22 +4949,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -4973,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -4991,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB30" s="1">
         <v>0</v>
@@ -5054,22 +5066,22 @@
     </row>
     <row r="31" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1">
-        <v>264</v>
+        <v>860</v>
       </c>
       <c r="C31" s="1">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -5078,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -5195,22 +5207,22 @@
     </row>
     <row r="32" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B32" s="1">
-        <v>212</v>
+        <v>818</v>
       </c>
       <c r="C32" s="1">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -5219,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -5231,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1">
         <v>0</v>
@@ -5255,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V32" s="1">
         <v>0</v>
@@ -5336,79 +5348,79 @@
     </row>
     <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B33" s="1">
-        <v>212</v>
+        <v>810</v>
       </c>
       <c r="C33" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="1">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>2</v>
+      </c>
+      <c r="M33" s="1">
+        <v>8</v>
+      </c>
+      <c r="N33" s="1">
+        <v>4</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="W33" s="1">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="1">
         <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>7</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
-      <c r="W33" s="1">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>0</v>
       </c>
       <c r="Z33" s="1">
         <v>0</v>
@@ -5477,13 +5489,13 @@
     </row>
     <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="B34" s="1">
-        <v>210</v>
+        <v>800</v>
       </c>
       <c r="C34" s="1">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -5492,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -5501,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
@@ -5513,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -5618,22 +5630,22 @@
     </row>
     <row r="35" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="B35" s="1">
-        <v>182</v>
+        <v>776</v>
       </c>
       <c r="C35" s="1">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F35" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -5642,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
@@ -5654,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N35" s="1">
         <v>0</v>
@@ -5759,22 +5771,22 @@
     </row>
     <row r="36" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1">
-        <v>180</v>
+        <v>725</v>
       </c>
       <c r="C36" s="1">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E36" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F36" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -5783,10 +5795,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -5795,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -5819,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -5900,22 +5912,22 @@
     </row>
     <row r="37" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1">
-        <v>162</v>
+        <v>724</v>
       </c>
       <c r="C37" s="1">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -5933,10 +5945,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37" s="1">
         <v>0</v>
@@ -5960,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="U37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -5969,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="X37" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -6041,22 +6053,22 @@
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1">
-        <v>161</v>
+        <v>695</v>
       </c>
       <c r="C38" s="1">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
@@ -6065,55 +6077,55 @@
         <v>0</v>
       </c>
       <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>5</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
         <v>1</v>
       </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>3</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-      <c r="U38" s="1">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
-      </c>
-      <c r="W38" s="1">
-        <v>0</v>
-      </c>
       <c r="X38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="1">
         <v>0</v>
@@ -6182,35 +6194,35 @@
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1">
-        <v>161</v>
+        <v>689</v>
       </c>
       <c r="C39" s="1">
+        <v>36</v>
+      </c>
+      <c r="D39" s="1">
+        <v>13</v>
+      </c>
+      <c r="E39" s="1">
         <v>7</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="F39" s="1">
         <v>3</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
         <v>1</v>
       </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0</v>
-      </c>
       <c r="K39" s="1">
         <v>0</v>
       </c>
@@ -6218,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N39" s="1">
         <v>0</v>
@@ -6251,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="X39" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
@@ -6323,22 +6335,22 @@
     </row>
     <row r="40" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1">
-        <v>160</v>
+        <v>684</v>
       </c>
       <c r="C40" s="1">
+        <v>40</v>
+      </c>
+      <c r="D40" s="1">
         <v>13</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -6359,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N40" s="1">
         <v>0</v>
@@ -6380,10 +6392,10 @@
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -6464,106 +6476,106 @@
     </row>
     <row r="41" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1">
-        <v>155</v>
+        <v>656</v>
       </c>
       <c r="C41" s="1">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F41" s="1">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>4</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="1">
         <v>3</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-      <c r="N41" s="1">
-        <v>1</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
-      <c r="S41" s="1">
-        <v>0</v>
-      </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
-      <c r="U41" s="1">
-        <v>0</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0</v>
-      </c>
-      <c r="W41" s="1">
-        <v>0</v>
-      </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="1">
-        <v>0</v>
       </c>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
@@ -6605,106 +6617,106 @@
     </row>
     <row r="42" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B42" s="1">
-        <v>132</v>
+        <v>626</v>
       </c>
       <c r="C42" s="1">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1">
+        <v>17</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="1">
+      <c r="Y42" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="1">
         <v>3</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="1">
-        <v>0</v>
       </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -6746,46 +6758,46 @@
     </row>
     <row r="43" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="B43" s="1">
-        <v>130</v>
+        <v>620</v>
       </c>
       <c r="C43" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
         <v>6</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
       <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
         <v>1</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
-        <v>0</v>
-      </c>
-      <c r="K43" s="1">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -6806,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -6830,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>
@@ -6842,10 +6854,10 @@
         <v>0</v>
       </c>
       <c r="AG43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
@@ -6887,31 +6899,31 @@
     </row>
     <row r="44" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B44" s="1">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="C44" s="1">
+        <v>51</v>
+      </c>
+      <c r="D44" s="1">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>16</v>
+      </c>
+      <c r="F44" s="1">
         <v>4</v>
       </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
-        <v>0</v>
-      </c>
-      <c r="F44" s="1">
-        <v>3</v>
-      </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I44" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="1">
         <v>0</v>
@@ -6926,37 +6938,37 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>5</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>4</v>
+      </c>
+      <c r="X44" s="1">
         <v>1</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-      <c r="X44" s="1">
-        <v>0</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -7028,91 +7040,91 @@
     </row>
     <row r="45" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1">
-        <v>116</v>
+        <v>573</v>
       </c>
       <c r="C45" s="1">
+        <v>22</v>
+      </c>
+      <c r="D45" s="1">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="1">
         <v>5</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
         <v>3</v>
-      </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>2</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="1">
-        <v>0</v>
-      </c>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
-      <c r="U45" s="1">
-        <v>0</v>
-      </c>
-      <c r="V45" s="1">
-        <v>0</v>
-      </c>
-      <c r="W45" s="1">
-        <v>0</v>
-      </c>
-      <c r="X45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="1">
-        <v>0</v>
       </c>
       <c r="AD45" s="1">
         <v>0</v>
@@ -7169,19 +7181,19 @@
     </row>
     <row r="46" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B46" s="1">
-        <v>114</v>
+        <v>537</v>
       </c>
       <c r="C46" s="1">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -7193,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="1">
         <v>0</v>
@@ -7205,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N46" s="1">
         <v>0</v>
@@ -7229,28 +7241,28 @@
         <v>0</v>
       </c>
       <c r="U46" s="1">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
         <v>1</v>
       </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
-      <c r="W46" s="1">
-        <v>2</v>
-      </c>
-      <c r="X46" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
       <c r="AB46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" s="1">
         <v>0</v>
@@ -7310,22 +7322,22 @@
     </row>
     <row r="47" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B47" s="1">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C47" s="1">
+        <v>27</v>
+      </c>
+      <c r="D47" s="1">
+        <v>5</v>
+      </c>
+      <c r="E47" s="1">
         <v>8</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
-        <v>6</v>
-      </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -7334,17 +7346,17 @@
         <v>0</v>
       </c>
       <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
         <v>2</v>
       </c>
-      <c r="J47" s="1">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
       <c r="M47" s="1">
         <v>0</v>
       </c>
@@ -7370,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="1">
         <v>0</v>
@@ -7379,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -7391,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
@@ -7451,47 +7463,47 @@
     </row>
     <row r="48" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B48" s="1">
-        <v>110</v>
+        <v>520</v>
       </c>
       <c r="C48" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
       </c>
       <c r="F48" s="1">
+        <v>7</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2</v>
+      </c>
+      <c r="N48" s="1">
         <v>3</v>
       </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1">
-        <v>0</v>
-      </c>
-      <c r="M48" s="1">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
       <c r="O48" s="1">
         <v>0</v>
       </c>
@@ -7511,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -7592,34 +7604,34 @@
     </row>
     <row r="49" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1">
-        <v>110</v>
+        <v>492</v>
       </c>
       <c r="C49" s="1">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E49" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
         <v>3</v>
       </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -7628,7 +7640,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" s="1">
         <v>0</v>
@@ -7652,19 +7664,19 @@
         <v>0</v>
       </c>
       <c r="U49" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
@@ -7733,79 +7745,79 @@
     </row>
     <row r="50" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B50" s="1">
-        <v>107</v>
+        <v>460</v>
       </c>
       <c r="C50" s="1">
+        <v>27</v>
+      </c>
+      <c r="D50" s="1">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
         <v>5</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="1">
         <v>1</v>
-      </c>
-      <c r="F50" s="1">
-        <v>1</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <v>1</v>
-      </c>
-      <c r="M50" s="1">
-        <v>1</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
-      <c r="V50" s="1">
-        <v>0</v>
-      </c>
-      <c r="W50" s="1">
-        <v>0</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="1">
-        <v>0</v>
       </c>
       <c r="Z50" s="1">
         <v>0</v>
@@ -7874,19 +7886,19 @@
     </row>
     <row r="51" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B51" s="1">
-        <v>102</v>
+        <v>456</v>
       </c>
       <c r="C51" s="1">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D51" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F51" s="1">
         <v>2</v>
@@ -7895,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -7913,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -8015,88 +8027,88 @@
     </row>
     <row r="52" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="B52" s="1">
-        <v>100</v>
+        <v>442</v>
       </c>
       <c r="C52" s="1">
+        <v>17</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>7</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
         <v>4</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1">
+      <c r="Y52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1">
         <v>3</v>
       </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
+      <c r="AB52" s="1">
         <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
-        <v>0</v>
-      </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
-      <c r="X52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="1">
-        <v>0</v>
       </c>
       <c r="AC52" s="1">
         <v>0</v>
@@ -8156,22 +8168,22 @@
     </row>
     <row r="53" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B53" s="1">
-        <v>90</v>
+        <v>418</v>
       </c>
       <c r="C53" s="1">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E53" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
@@ -8189,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M53" s="1">
         <v>0</v>
@@ -8255,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="AH53" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
@@ -8297,22 +8309,22 @@
     </row>
     <row r="54" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B54" s="1">
-        <v>86</v>
+        <v>394</v>
       </c>
       <c r="C54" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -8321,10 +8333,10 @@
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -8333,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N54" s="1">
         <v>0</v>
@@ -8438,28 +8450,28 @@
     </row>
     <row r="55" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B55" s="1">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="C55" s="1">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E55" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -8474,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="1">
         <v>0</v>
@@ -8504,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="1">
         <v>0</v>
@@ -8579,67 +8591,67 @@
     </row>
     <row r="56" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>72</v>
+        <v>364</v>
       </c>
       <c r="C56" s="1">
+        <v>28</v>
+      </c>
+      <c r="D56" s="1">
+        <v>13</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="F56" s="1">
+        <v>8</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
         <v>5</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="F56" s="1">
-        <v>2</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
-        <v>2</v>
       </c>
       <c r="V56" s="1">
         <v>0</v>
@@ -8720,31 +8732,31 @@
     </row>
     <row r="57" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="B57" s="1">
-        <v>71</v>
+        <v>359</v>
       </c>
       <c r="C57" s="1">
+        <v>28</v>
+      </c>
+      <c r="D57" s="1">
+        <v>13</v>
+      </c>
+      <c r="E57" s="1">
         <v>4</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="F57" s="1">
+        <v>4</v>
+      </c>
+      <c r="G57" s="1">
         <v>3</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
       <c r="H57" s="1">
         <v>0</v>
       </c>
       <c r="I57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -8753,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -8861,22 +8873,22 @@
     </row>
     <row r="58" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="B58" s="1">
-        <v>70</v>
+        <v>358</v>
       </c>
       <c r="C58" s="1">
+        <v>25</v>
+      </c>
+      <c r="D58" s="1">
+        <v>13</v>
+      </c>
+      <c r="E58" s="1">
         <v>4</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
       <c r="F58" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -8885,10 +8897,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -8921,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="1">
         <v>0</v>
@@ -9002,22 +9014,22 @@
     </row>
     <row r="59" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B59" s="1">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="C59" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -9062,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="1">
         <v>0</v>
@@ -9083,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="1">
         <v>0</v>
@@ -9143,19 +9155,19 @@
     </row>
     <row r="60" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1">
-        <v>70</v>
+        <v>348</v>
       </c>
       <c r="C60" s="1">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1">
+        <v>13</v>
+      </c>
+      <c r="E60" s="1">
         <v>4</v>
-      </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0</v>
       </c>
       <c r="F60" s="1">
         <v>3</v>
@@ -9167,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="1">
         <v>0</v>
@@ -9179,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="1">
         <v>0</v>
@@ -9203,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
@@ -9284,22 +9296,22 @@
     </row>
     <row r="61" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B61" s="1">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="C61" s="1">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -9323,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -9383,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="AH61" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
@@ -9425,22 +9437,22 @@
     </row>
     <row r="62" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="B62" s="1">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="C62" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -9449,10 +9461,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -9461,10 +9473,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -9566,22 +9578,22 @@
     </row>
     <row r="63" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="B63" s="1">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="C63" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -9638,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="1">
         <v>0</v>
@@ -9707,19 +9719,19 @@
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B64" s="1">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="C64" s="1">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D64" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -9728,7 +9740,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -9770,10 +9782,10 @@
         <v>0</v>
       </c>
       <c r="V64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" s="1">
         <v>0</v>
@@ -9848,22 +9860,22 @@
     </row>
     <row r="65" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B65" s="1">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="C65" s="1">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F65" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -9872,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" s="1">
         <v>0</v>
@@ -9989,22 +10001,22 @@
     </row>
     <row r="66" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B66" s="1">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="C66" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -10049,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" s="1">
         <v>0</v>
@@ -10058,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -10130,22 +10142,22 @@
     </row>
     <row r="67" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="B67" s="1">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="C67" s="1">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
@@ -10271,19 +10283,19 @@
     </row>
     <row r="68" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B68" s="1">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="C68" s="1">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E68" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -10307,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" s="1">
         <v>0</v>
@@ -10331,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V68" s="1">
         <v>0</v>
@@ -10412,19 +10424,19 @@
     </row>
     <row r="69" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B69" s="1">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="C69" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E69" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -10472,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V69" s="1">
         <v>0</v>
@@ -10511,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="AH69" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
@@ -10553,22 +10565,22 @@
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B70" s="1">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C70" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D70" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -10613,7 +10625,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V70" s="1">
         <v>0</v>
@@ -10694,22 +10706,22 @@
     </row>
     <row r="71" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B71" s="1">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C71" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -10754,7 +10766,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V71" s="1">
         <v>0</v>
@@ -10835,19 +10847,19 @@
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="B72" s="1">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="C72" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -10895,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V72" s="1">
         <v>0</v>
@@ -10976,19 +10988,19 @@
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B73" s="1">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="C73" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -11036,7 +11048,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V73" s="1">
         <v>0</v>
@@ -11117,19 +11129,19 @@
     </row>
     <row r="74" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B74" s="1">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="C74" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E74" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -11177,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
@@ -11186,7 +11198,7 @@
         <v>2</v>
       </c>
       <c r="X74" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y74" s="1">
         <v>0</v>
@@ -11258,23 +11270,23 @@
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="C75" s="1">
+        <v>13</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1">
         <v>3</v>
       </c>
-      <c r="D75" s="1">
-        <v>0</v>
-      </c>
-      <c r="E75" s="1">
-        <v>2</v>
-      </c>
-      <c r="F75" s="1">
-        <v>1</v>
-      </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
@@ -11315,10 +11327,10 @@
         <v>0</v>
       </c>
       <c r="T75" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U75" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -11399,13 +11411,13 @@
     </row>
     <row r="76" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="B76" s="1">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="C76" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
@@ -11414,31 +11426,31 @@
         <v>2</v>
       </c>
       <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
         <v>1</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
-        <v>0</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-      <c r="L76" s="1">
-        <v>0</v>
-      </c>
-      <c r="M76" s="1">
-        <v>0</v>
-      </c>
-      <c r="N76" s="1">
-        <v>0</v>
       </c>
       <c r="O76" s="1">
         <v>0</v>
@@ -11540,19 +11552,19 @@
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B77" s="1">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C77" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E77" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -11681,22 +11693,22 @@
     </row>
     <row r="78" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B78" s="1">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C78" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -11741,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" s="1">
         <v>0</v>
@@ -11822,79 +11834,79 @@
     </row>
     <row r="79" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B79" s="1">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="C79" s="1">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>0</v>
+      </c>
+      <c r="R79" s="1">
+        <v>0</v>
+      </c>
+      <c r="S79" s="1">
+        <v>0</v>
+      </c>
+      <c r="T79" s="1">
+        <v>0</v>
+      </c>
+      <c r="U79" s="1">
+        <v>0</v>
+      </c>
+      <c r="V79" s="1">
+        <v>0</v>
+      </c>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+      <c r="X79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="1">
         <v>1</v>
-      </c>
-      <c r="D79" s="1">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1">
-        <v>1</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0</v>
-      </c>
-      <c r="J79" s="1">
-        <v>0</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" s="1">
-        <v>0</v>
-      </c>
-      <c r="M79" s="1">
-        <v>0</v>
-      </c>
-      <c r="N79" s="1">
-        <v>0</v>
-      </c>
-      <c r="O79" s="1">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="1">
-        <v>0</v>
-      </c>
-      <c r="R79" s="1">
-        <v>0</v>
-      </c>
-      <c r="S79" s="1">
-        <v>0</v>
-      </c>
-      <c r="T79" s="1">
-        <v>0</v>
-      </c>
-      <c r="U79" s="1">
-        <v>0</v>
-      </c>
-      <c r="V79" s="1">
-        <v>0</v>
-      </c>
-      <c r="W79" s="1">
-        <v>0</v>
-      </c>
-      <c r="X79" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="1">
-        <v>0</v>
       </c>
       <c r="Z79" s="1">
         <v>0</v>
@@ -11963,19 +11975,19 @@
     </row>
     <row r="80" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B80" s="1">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C80" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -12023,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V80" s="1">
         <v>0</v>
@@ -12104,28 +12116,28 @@
     </row>
     <row r="81" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="B81" s="1">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="C81" s="1">
+        <v>5</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
         <v>1</v>
       </c>
-      <c r="D81" s="1">
-        <v>0</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
@@ -12140,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="1">
         <v>0</v>
@@ -12164,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="1">
         <v>0</v>
@@ -12245,22 +12257,22 @@
     </row>
     <row r="82" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B82" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -12305,7 +12317,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V82" s="1">
         <v>0</v>
@@ -12386,13 +12398,13 @@
     </row>
     <row r="83" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B83" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C83" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
@@ -12446,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V83" s="1">
         <v>0</v>
@@ -12527,16 +12539,16 @@
     </row>
     <row r="84" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B84" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -12668,13 +12680,13 @@
     </row>
     <row r="85" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B85" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -12722,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T85" s="1">
         <v>0</v>
@@ -12809,13 +12821,13 @@
     </row>
     <row r="86" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B86" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C86" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -12869,7 +12881,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V86" s="1">
         <v>0</v>
@@ -12950,19 +12962,19 @@
     </row>
     <row r="87" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B87" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C87" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -13091,22 +13103,22 @@
     </row>
     <row r="88" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="B88" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C88" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="1">
         <v>0</v>
@@ -13231,12 +13243,14 @@
       <c r="BW88" s="1"/>
     </row>
     <row r="89" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
+      <c r="A89" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="B89" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -13290,7 +13304,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V89" s="1">
         <v>0</v>
@@ -13370,12 +13384,14 @@
       <c r="BW89" s="1"/>
     </row>
     <row r="90" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
+      <c r="A90" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="B90" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
@@ -13429,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" s="1">
         <v>0</v>
@@ -13509,7 +13525,9 @@
       <c r="BW90" s="1"/>
     </row>
     <row r="91" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
+      <c r="A91" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="B91" s="1">
         <v>0</v>
       </c>
@@ -13648,7 +13666,9 @@
       <c r="BW91" s="1"/>
     </row>
     <row r="92" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
+      <c r="A92" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="B92" s="1">
         <v>0</v>
       </c>

--- a/Results2.xlsx
+++ b/Results2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B2F926-70EC-4A06-ADCC-E85D2FFE294C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C3B47C-2FE5-4464-AD4D-0D31F97857BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2132F57B-8824-4764-BC02-18EC8AEFAB7F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Epic Fenrir Squad</t>
   </si>
   <si>
-    <t>Epic Inferno Squad</t>
-  </si>
-  <si>
     <t>Union of Triumph Personal Reward</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>Ayanen</t>
   </si>
   <si>
-    <t>Bathris II</t>
-  </si>
-  <si>
     <t>Beve</t>
   </si>
   <si>
@@ -148,9 +142,6 @@
   </si>
   <si>
     <t>BOKIKI</t>
-  </si>
-  <si>
-    <t>BrethAlyzer</t>
   </si>
   <si>
     <t>Brewski</t>
@@ -195,9 +186,6 @@
     <t>Furious Styles</t>
   </si>
   <si>
-    <t>Gelu Graniceru</t>
-  </si>
-  <si>
     <t>GibsFR1908</t>
   </si>
   <si>
@@ -228,9 +216,6 @@
     <t>LamazhruN</t>
   </si>
   <si>
-    <t>LoGaN</t>
-  </si>
-  <si>
     <t>Luchanel</t>
   </si>
   <si>
@@ -247,9 +232,6 @@
   </si>
   <si>
     <t>Mareks</t>
-  </si>
-  <si>
-    <t>MARS</t>
   </si>
   <si>
     <t>Massinissa</t>
@@ -330,13 +312,7 @@
     <t>Serdriel</t>
   </si>
   <si>
-    <t>SilentGrim</t>
-  </si>
-  <si>
     <t>SkayRrraVantaXx</t>
-  </si>
-  <si>
-    <t>Starshij Brat</t>
   </si>
   <si>
     <t>Sundown</t>
@@ -355,9 +331,6 @@
   </si>
   <si>
     <t>Ulf Vidar</t>
-  </si>
-  <si>
-    <t>Valea Jiului</t>
   </si>
   <si>
     <t>Valka</t>
@@ -387,9 +360,6 @@
     <t>Zorrillo</t>
   </si>
   <si>
-    <t>MaeTWF</t>
-  </si>
-  <si>
     <t>Jahannm</t>
   </si>
   <si>
@@ -400,6 +370,63 @@
   </si>
   <si>
     <t>Ragefury</t>
+  </si>
+  <si>
+    <t>Epic jormungandr Squad</t>
+  </si>
+  <si>
+    <t>Bavmorda</t>
+  </si>
+  <si>
+    <t>Brother D</t>
+  </si>
+  <si>
+    <t>Dario</t>
+  </si>
+  <si>
+    <t>DORIS</t>
+  </si>
+  <si>
+    <t>Fearlessbeard</t>
+  </si>
+  <si>
+    <t>Mae TWF</t>
+  </si>
+  <si>
+    <t>Mavenn</t>
+  </si>
+  <si>
+    <t>Maxi Spell</t>
+  </si>
+  <si>
+    <t>Medusa</t>
+  </si>
+  <si>
+    <t>Mel</t>
+  </si>
+  <si>
+    <t>Olninod jr</t>
+  </si>
+  <si>
+    <t>Petr</t>
+  </si>
+  <si>
+    <t>RAIN jr</t>
+  </si>
+  <si>
+    <t>Rufur</t>
+  </si>
+  <si>
+    <t>sacit</t>
+  </si>
+  <si>
+    <t>Tomiris</t>
+  </si>
+  <si>
+    <t>turia</t>
+  </si>
+  <si>
+    <t>Turrosan</t>
   </si>
 </sst>
 </file>
@@ -450,9 +477,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -798,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ACA3018-E49A-49B2-AB2D-E7B776AEAC6B}">
-  <dimension ref="A1:BW100"/>
+  <dimension ref="A1:BW101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -887,16 +915,16 @@
         <v>23</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>16</v>
@@ -920,22 +948,22 @@
         <v>22</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
@@ -977,19 +1005,19 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1">
-        <v>4716</v>
+        <v>6013</v>
       </c>
       <c r="C2" s="1">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="D2" s="1">
         <v>5</v>
       </c>
       <c r="E2" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1">
         <v>96</v>
@@ -1001,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1">
         <v>1</v>
@@ -1019,22 +1047,22 @@
         <v>15</v>
       </c>
       <c r="O2" s="1">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
         <v>2</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1">
-        <v>0</v>
-      </c>
       <c r="S2" s="1">
         <v>0</v>
       </c>
       <c r="T2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
@@ -1064,7 +1092,7 @@
         <v>6</v>
       </c>
       <c r="AD2" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE2" s="1">
         <v>0</v>
@@ -1118,31 +1146,31 @@
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1">
-        <v>3538</v>
+        <v>5041</v>
       </c>
       <c r="C3" s="1">
-        <v>189</v>
+        <v>337</v>
       </c>
       <c r="D3" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -1151,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
@@ -1166,40 +1194,40 @@
         <v>0</v>
       </c>
       <c r="Q3" s="1">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="R3" s="1">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S3" s="1">
         <v>0</v>
       </c>
       <c r="T3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="1">
         <v>0</v>
       </c>
       <c r="AA3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="1">
         <v>0</v>
@@ -1259,22 +1287,22 @@
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1">
-        <v>2980</v>
+        <v>4567</v>
       </c>
       <c r="C4" s="1">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1283,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -1295,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N4" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O4" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P4" s="1">
         <v>0</v>
@@ -1316,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U4" s="1">
         <v>0</v>
@@ -1328,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y4" s="1">
         <v>0</v>
@@ -1400,64 +1428,64 @@
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B5" s="1">
-        <v>2349</v>
+        <v>4217</v>
       </c>
       <c r="C5" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N5" s="1">
+        <v>4</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
         <v>6</v>
       </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
       <c r="T5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
@@ -1466,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
@@ -1478,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -1496,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="AG5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5" s="1">
         <v>3</v>
@@ -1541,43 +1569,43 @@
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1">
-        <v>1971</v>
+        <v>3812</v>
       </c>
       <c r="C6" s="1">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M6" s="1">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
@@ -1598,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U6" s="1">
         <v>0</v>
@@ -1607,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X6" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -1682,13 +1710,13 @@
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
-        <v>1930</v>
+        <v>3618</v>
       </c>
       <c r="C7" s="1">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
@@ -1697,25 +1725,25 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -1724,25 +1752,25 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
         <v>5</v>
       </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
       <c r="U7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1751,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="1">
         <v>0</v>
@@ -1763,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
@@ -1823,55 +1851,55 @@
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1">
-        <v>1892</v>
+        <v>3542</v>
       </c>
       <c r="C8" s="1">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -1880,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U8" s="1">
         <v>0</v>
@@ -1889,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -1901,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
@@ -1964,106 +1992,106 @@
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1">
-        <v>1873</v>
+        <v>3320</v>
       </c>
       <c r="C9" s="1">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>39</v>
+      </c>
+      <c r="K9" s="1">
+        <v>4</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>13</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>5</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="1">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1">
-        <v>9</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>9</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1">
         <v>3</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
-      </c>
-      <c r="W9" s="1">
-        <v>3</v>
-      </c>
-      <c r="X9" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>7</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>0</v>
       </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -2105,22 +2133,22 @@
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1">
-        <v>1830</v>
+        <v>3246</v>
       </c>
       <c r="C10" s="1">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2129,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -2144,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O10" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -2162,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
@@ -2177,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="1">
         <v>0</v>
@@ -2192,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="1">
         <v>0</v>
@@ -2246,22 +2274,22 @@
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="B11" s="1">
-        <v>1809</v>
+        <v>2544</v>
       </c>
       <c r="C11" s="1">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2270,25 +2298,25 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J11" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2303,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -2315,10 +2343,10 @@
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
         <v>0</v>
@@ -2330,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="1">
         <v>0</v>
@@ -2345,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -2387,22 +2415,22 @@
     </row>
     <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1">
-        <v>1600</v>
+        <v>2468</v>
       </c>
       <c r="C12" s="1">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1">
         <v>13</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2411,25 +2439,25 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
@@ -2444,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
@@ -2456,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2486,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -2528,91 +2556,91 @@
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1">
-        <v>1498</v>
+        <v>2450</v>
       </c>
       <c r="C13" s="1">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
+        <v>47</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>17</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>24</v>
+      </c>
+      <c r="N13" s="1">
+        <v>6</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>5</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
+        <v>30</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="1">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>14</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>4</v>
-      </c>
-      <c r="N13" s="1">
-        <v>4</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
-        <v>0</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
@@ -2627,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2669,85 +2697,85 @@
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1">
-        <v>1440</v>
+        <v>2435</v>
       </c>
       <c r="C14" s="1">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
+        <v>34</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>36</v>
+      </c>
+      <c r="I14" s="1">
+        <v>7</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>19</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>5</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
         <v>6</v>
       </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>9</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>11</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>5</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
       <c r="Y14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="1">
         <v>0</v>
       </c>
       <c r="AA14" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB14" s="1">
         <v>0</v>
@@ -2810,64 +2838,64 @@
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1">
-        <v>1430</v>
+        <v>2402</v>
       </c>
       <c r="C15" s="1">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1">
         <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>27</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
         <v>5</v>
       </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>4</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
       <c r="R15" s="1">
         <v>0</v>
       </c>
       <c r="S15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
@@ -2876,22 +2904,22 @@
         <v>0</v>
       </c>
       <c r="W15" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X15" s="1">
         <v>8</v>
       </c>
       <c r="Y15" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="1">
         <v>0</v>
       </c>
       <c r="AA15" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="1">
         <v>0</v>
@@ -2909,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2951,50 +2979,50 @@
     </row>
     <row r="16" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="1">
-        <v>1392</v>
+        <v>2395</v>
       </c>
       <c r="C16" s="1">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="D16" s="1">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>3</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="1">
-        <v>31</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>3</v>
-      </c>
-      <c r="M16" s="1">
-        <v>21</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
       <c r="P16" s="1">
         <v>0</v>
       </c>
@@ -3002,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="R16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="1">
         <v>0</v>
       </c>
       <c r="T16" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U16" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -3023,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z16" s="1">
         <v>0</v>
@@ -3035,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="1">
         <v>0</v>
@@ -3047,10 +3075,10 @@
         <v>0</v>
       </c>
       <c r="AG16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -3092,22 +3120,22 @@
     </row>
     <row r="17" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B17" s="1">
-        <v>1310</v>
+        <v>2301</v>
       </c>
       <c r="C17" s="1">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="D17" s="1">
         <v>13</v>
       </c>
       <c r="E17" s="1">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3116,40 +3144,40 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>51</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
         <v>5</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>2</v>
-      </c>
-      <c r="N17" s="1">
-        <v>5</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
@@ -3233,22 +3261,22 @@
     </row>
     <row r="18" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B18" s="1">
-        <v>1287</v>
+        <v>2194</v>
       </c>
       <c r="C18" s="1">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="F18" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -3257,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -3269,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N18" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -3290,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="T18" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -3302,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -3311,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="1">
         <v>0</v>
@@ -3374,64 +3402,64 @@
     </row>
     <row r="19" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B19" s="1">
-        <v>1280</v>
+        <v>1993</v>
       </c>
       <c r="C19" s="1">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>8</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>41</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
         <v>1</v>
       </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>10</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="O19" s="1">
-        <v>6</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
       <c r="S19" s="1">
         <v>0</v>
       </c>
       <c r="T19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" s="1">
         <v>0</v>
@@ -3452,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB19" s="1">
         <v>0</v>
@@ -3515,23 +3543,23 @@
     </row>
     <row r="20" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>1220</v>
+        <v>1970</v>
       </c>
       <c r="C20" s="1">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
         <v>4</v>
       </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>7</v>
-      </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
@@ -3542,10 +3570,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -3554,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -3563,16 +3591,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="1">
         <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -3587,10 +3615,10 @@
         <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z20" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
@@ -3602,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3656,22 +3684,22 @@
     </row>
     <row r="21" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B21" s="1">
-        <v>1174</v>
+        <v>1933</v>
       </c>
       <c r="C21" s="1">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F21" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -3680,41 +3708,41 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
+        <v>7</v>
+      </c>
+      <c r="J21" s="1">
+        <v>3</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>17</v>
+      </c>
+      <c r="N21" s="1">
+        <v>3</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
         <v>5</v>
       </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>2</v>
-      </c>
-      <c r="N21" s="1">
-        <v>9</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
       <c r="U21" s="1">
         <v>0</v>
       </c>
@@ -3725,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -3734,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="AA21" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AB21" s="1">
         <v>0</v>
@@ -3797,19 +3825,19 @@
     </row>
     <row r="22" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B22" s="1">
-        <v>1139</v>
+        <v>1880</v>
       </c>
       <c r="C22" s="1">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3821,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
@@ -3833,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -3845,16 +3873,16 @@
         <v>0</v>
       </c>
       <c r="Q22" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R22" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S22" s="1">
         <v>0</v>
       </c>
       <c r="T22" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
@@ -3875,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3938,106 +3966,106 @@
     </row>
     <row r="23" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1">
-        <v>1121</v>
+        <v>1845</v>
       </c>
       <c r="C23" s="1">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
       </c>
       <c r="E23" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F23" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" s="1">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>4</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>1</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>5</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="1">
         <v>3</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>9</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>1</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="1">
-        <v>2</v>
-      </c>
-      <c r="X23" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>6</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="1">
-        <v>0</v>
       </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -4079,19 +4107,19 @@
     </row>
     <row r="24" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="B24" s="1">
-        <v>1084</v>
+        <v>1818</v>
       </c>
       <c r="C24" s="1">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4103,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J24" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4136,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U24" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -4148,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="1">
         <v>0</v>
@@ -4160,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="1">
         <v>0</v>
@@ -4220,22 +4248,22 @@
     </row>
     <row r="25" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="B25" s="1">
-        <v>910</v>
+        <v>1789</v>
       </c>
       <c r="C25" s="1">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F25" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -4244,64 +4272,64 @@
         <v>0</v>
       </c>
       <c r="I25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>9</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1">
+        <v>5</v>
+      </c>
+      <c r="U25" s="1">
         <v>1</v>
       </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>8</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
         <v>2</v>
       </c>
-      <c r="V25" s="1">
-        <v>0</v>
-      </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
       <c r="X25" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
         <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4361,56 +4389,56 @@
     </row>
     <row r="26" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B26" s="1">
-        <v>910</v>
+        <v>1785</v>
       </c>
       <c r="C26" s="1">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D26" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>3</v>
+      </c>
+      <c r="K26" s="1">
+        <v>5</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>2</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>8</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>8</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
       <c r="R26" s="1">
         <v>0</v>
       </c>
@@ -4418,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -4427,16 +4455,16 @@
         <v>0</v>
       </c>
       <c r="W26" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z26" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA26" s="1">
         <v>0</v>
@@ -4502,13 +4530,13 @@
     </row>
     <row r="27" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B27" s="1">
-        <v>905</v>
+        <v>1675</v>
       </c>
       <c r="C27" s="1">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
@@ -4517,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -4526,32 +4554,32 @@
         <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
         <v>2</v>
       </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
       <c r="L27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
         <v>1</v>
       </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
       <c r="R27" s="1">
         <v>0</v>
       </c>
@@ -4559,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
@@ -4571,22 +4599,22 @@
         <v>0</v>
       </c>
       <c r="X27" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y27" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z27" s="1">
         <v>0</v>
       </c>
       <c r="AA27" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="1">
         <v>0</v>
@@ -4643,88 +4671,88 @@
     </row>
     <row r="28" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1">
-        <v>901</v>
+        <v>1660</v>
       </c>
       <c r="C28" s="1">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>18</v>
+      </c>
+      <c r="J28" s="1">
         <v>3</v>
       </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>10</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>5</v>
+      </c>
+      <c r="U28" s="1">
+        <v>2</v>
+      </c>
+      <c r="V28" s="1">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="1">
         <v>1</v>
       </c>
-      <c r="K28" s="1">
+      <c r="Z28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
         <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>3</v>
-      </c>
-      <c r="N28" s="1">
-        <v>2</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-      <c r="S28" s="1">
-        <v>0</v>
-      </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
-      <c r="U28" s="1">
-        <v>0</v>
-      </c>
-      <c r="V28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="1">
-        <v>2</v>
-      </c>
-      <c r="X28" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="1">
-        <v>0</v>
       </c>
       <c r="AC28" s="1">
         <v>0</v>
@@ -4784,22 +4812,22 @@
     </row>
     <row r="29" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1">
-        <v>868</v>
+        <v>1630</v>
       </c>
       <c r="C29" s="1">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1">
         <v>13</v>
       </c>
       <c r="E29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -4811,19 +4839,19 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O29" s="1">
         <v>2</v>
@@ -4832,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
@@ -4841,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
@@ -4853,22 +4881,22 @@
         <v>0</v>
       </c>
       <c r="X29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
@@ -4880,10 +4908,10 @@
         <v>0</v>
       </c>
       <c r="AG29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
@@ -4925,85 +4953,85 @@
     </row>
     <row r="30" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="B30" s="1">
-        <v>867</v>
+        <v>1490</v>
       </c>
       <c r="C30" s="1">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
       </c>
       <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>9</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>11</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1">
+        <v>5</v>
+      </c>
+      <c r="U30" s="1">
+        <v>5</v>
+      </c>
+      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1">
         <v>2</v>
       </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>6</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>5</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1">
-        <v>0</v>
-      </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
-      <c r="U30" s="1">
-        <v>0</v>
-      </c>
-      <c r="V30" s="1">
-        <v>0</v>
-      </c>
-      <c r="W30" s="1">
-        <v>0</v>
-      </c>
-      <c r="X30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
       <c r="Z30" s="1">
         <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="1">
         <v>0</v>
@@ -5066,85 +5094,85 @@
     </row>
     <row r="31" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B31" s="1">
-        <v>860</v>
+        <v>1461</v>
       </c>
       <c r="C31" s="1">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D31" s="1">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>8</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>3</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>5</v>
+      </c>
+      <c r="N31" s="1">
+        <v>9</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
+        <v>5</v>
+      </c>
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
         <v>4</v>
       </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>28</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
-        <v>11</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="Y31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1">
         <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
-      <c r="U31" s="1">
-        <v>0</v>
-      </c>
-      <c r="V31" s="1">
-        <v>0</v>
-      </c>
-      <c r="W31" s="1">
-        <v>0</v>
-      </c>
-      <c r="X31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="1">
-        <v>0</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
@@ -5207,22 +5235,22 @@
     </row>
     <row r="32" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="B32" s="1">
-        <v>818</v>
+        <v>1434</v>
       </c>
       <c r="C32" s="1">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -5231,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -5246,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -5264,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U32" s="1">
         <v>0</v>
@@ -5348,79 +5376,79 @@
     </row>
     <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B33" s="1">
-        <v>810</v>
+        <v>1426</v>
       </c>
       <c r="C33" s="1">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1">
         <v>5</v>
       </c>
       <c r="E33" s="1">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="1">
+        <v>14</v>
+      </c>
+      <c r="N33" s="1">
+        <v>6</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1">
         <v>5</v>
       </c>
-      <c r="F33" s="1">
-        <v>4</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="W33" s="1">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="1">
         <v>2</v>
-      </c>
-      <c r="M33" s="1">
-        <v>8</v>
-      </c>
-      <c r="N33" s="1">
-        <v>4</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
-      <c r="W33" s="1">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>1</v>
       </c>
       <c r="Z33" s="1">
         <v>0</v>
@@ -5489,13 +5517,13 @@
     </row>
     <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B34" s="1">
-        <v>800</v>
+        <v>1370</v>
       </c>
       <c r="C34" s="1">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -5504,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -5516,7 +5544,7 @@
         <v>19</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -5528,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -5546,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="1">
         <v>0</v>
@@ -5630,91 +5658,91 @@
     </row>
     <row r="35" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B35" s="1">
-        <v>776</v>
+        <v>1369</v>
       </c>
       <c r="C35" s="1">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>8</v>
+      </c>
+      <c r="K35" s="1">
+        <v>2</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>5</v>
+      </c>
+      <c r="N35" s="1">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>3</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1">
+        <v>5</v>
+      </c>
+      <c r="T35" s="1">
+        <v>5</v>
+      </c>
+      <c r="U35" s="1">
+        <v>0</v>
+      </c>
+      <c r="V35" s="1">
+        <v>0</v>
+      </c>
+      <c r="W35" s="1">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1">
         <v>7</v>
       </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>10</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
-      </c>
-      <c r="W35" s="1">
-        <v>0</v>
-      </c>
-      <c r="X35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>0</v>
-      </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
       <c r="AC35" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD35" s="1">
         <v>0</v>
@@ -5771,10 +5799,10 @@
     </row>
     <row r="36" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1">
-        <v>725</v>
+        <v>1349</v>
       </c>
       <c r="C36" s="1">
         <v>56</v>
@@ -5783,7 +5811,7 @@
         <v>13</v>
       </c>
       <c r="E36" s="1">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -5795,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -5807,52 +5835,52 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
         <v>1</v>
       </c>
-      <c r="N36" s="1">
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="1">
+        <v>5</v>
+      </c>
+      <c r="U36" s="1">
+        <v>3</v>
+      </c>
+      <c r="V36" s="1">
+        <v>0</v>
+      </c>
+      <c r="W36" s="1">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1">
+        <v>18</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="1">
         <v>1</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
-      <c r="U36" s="1">
-        <v>4</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
-      <c r="W36" s="1">
-        <v>0</v>
-      </c>
-      <c r="X36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
       </c>
       <c r="AC36" s="1">
         <v>0</v>
@@ -5912,22 +5940,22 @@
     </row>
     <row r="37" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B37" s="1">
-        <v>724</v>
+        <v>1265</v>
       </c>
       <c r="C37" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -5939,22 +5967,22 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
         <v>2</v>
       </c>
-      <c r="N37" s="1">
-        <v>0</v>
-      </c>
       <c r="O37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -5969,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U37" s="1">
         <v>0</v>
@@ -5981,11 +6009,11 @@
         <v>0</v>
       </c>
       <c r="X37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="1">
         <v>2</v>
       </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
       <c r="Z37" s="1">
         <v>0</v>
       </c>
@@ -5996,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="AC37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD37" s="1">
         <v>0</v>
@@ -6011,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="AH37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -6053,29 +6081,29 @@
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1">
-        <v>695</v>
+        <v>1254</v>
       </c>
       <c r="C38" s="1">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
         <v>1</v>
       </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
@@ -6089,28 +6117,28 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
+        <v>10</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
         <v>5</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
       </c>
       <c r="U38" s="1">
         <v>0</v>
@@ -6122,10 +6150,10 @@
         <v>1</v>
       </c>
       <c r="X38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="1">
         <v>0</v>
@@ -6194,22 +6222,22 @@
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1">
-        <v>689</v>
+        <v>1235</v>
       </c>
       <c r="C39" s="1">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D39" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -6218,43 +6246,43 @@
         <v>0</v>
       </c>
       <c r="I39" s="1">
+        <v>15</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>4</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>1</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="1">
         <v>5</v>
       </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
       <c r="U39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -6263,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="X39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
@@ -6335,22 +6363,22 @@
     </row>
     <row r="40" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>684</v>
+        <v>1220</v>
       </c>
       <c r="C40" s="1">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" s="1">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -6359,19 +6387,19 @@
         <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N40" s="1">
         <v>0</v>
@@ -6383,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -6392,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
@@ -6404,10 +6432,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z40" s="1">
         <v>0</v>
@@ -6476,22 +6504,22 @@
     </row>
     <row r="41" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B41" s="1">
-        <v>656</v>
+        <v>1204</v>
       </c>
       <c r="C41" s="1">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
@@ -6500,32 +6528,32 @@
         <v>0</v>
       </c>
       <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>11</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>10</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
         <v>2</v>
       </c>
-      <c r="J41" s="1">
-        <v>2</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>4</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
       <c r="R41" s="1">
         <v>0</v>
       </c>
@@ -6533,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
@@ -6575,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="AH41" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
@@ -6617,22 +6645,22 @@
     </row>
     <row r="42" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B42" s="1">
-        <v>626</v>
+        <v>1177</v>
       </c>
       <c r="C42" s="1">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D42" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -6641,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
@@ -6650,13 +6678,13 @@
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -6674,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
@@ -6686,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="1">
         <v>0</v>
@@ -6716,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -6758,22 +6786,22 @@
     </row>
     <row r="43" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B43" s="1">
-        <v>620</v>
+        <v>1170</v>
       </c>
       <c r="C43" s="1">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D43" s="1">
         <v>13</v>
       </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -6782,67 +6810,67 @@
         <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
         <v>2</v>
       </c>
-      <c r="K43" s="1">
-        <v>0</v>
-      </c>
       <c r="L43" s="1">
         <v>0</v>
       </c>
       <c r="M43" s="1">
+        <v>4</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>2</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>3</v>
+      </c>
+      <c r="R43" s="1">
         <v>1</v>
       </c>
-      <c r="N43" s="1">
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>5</v>
+      </c>
+      <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
         <v>2</v>
       </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
-      <c r="T43" s="1">
-        <v>0</v>
-      </c>
-      <c r="U43" s="1">
-        <v>0</v>
-      </c>
-      <c r="V43" s="1">
-        <v>0</v>
-      </c>
-      <c r="W43" s="1">
-        <v>0</v>
-      </c>
-      <c r="X43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="1">
-        <v>0</v>
-      </c>
       <c r="AC43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>
@@ -6854,10 +6882,10 @@
         <v>0</v>
       </c>
       <c r="AG43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
@@ -6899,76 +6927,76 @@
     </row>
     <row r="44" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B44" s="1">
-        <v>580</v>
+        <v>1078</v>
       </c>
       <c r="C44" s="1">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D44" s="1">
         <v>13</v>
       </c>
       <c r="E44" s="1">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>20</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>2</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
         <v>5</v>
       </c>
-      <c r="I44" s="1">
-        <v>2</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
       <c r="U44" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
       </c>
       <c r="W44" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -7040,46 +7068,46 @@
     </row>
     <row r="45" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B45" s="1">
-        <v>573</v>
+        <v>951</v>
       </c>
       <c r="C45" s="1">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D45" s="1">
         <v>13</v>
       </c>
       <c r="E45" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
         <v>1</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
-      </c>
       <c r="K45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -7097,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
@@ -7106,14 +7134,14 @@
         <v>0</v>
       </c>
       <c r="W45" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="1">
         <v>3</v>
       </c>
-      <c r="Y45" s="1">
-        <v>5</v>
-      </c>
       <c r="Z45" s="1">
         <v>0</v>
       </c>
@@ -7124,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="AC45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="1">
         <v>0</v>
@@ -7181,19 +7209,19 @@
     </row>
     <row r="46" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1">
-        <v>537</v>
+        <v>943</v>
       </c>
       <c r="C46" s="1">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -7205,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J46" s="1">
         <v>0</v>
@@ -7217,28 +7245,28 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
+        <v>9</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
         <v>5</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1">
-        <v>0</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
@@ -7322,67 +7350,67 @@
     </row>
     <row r="47" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="B47" s="1">
-        <v>536</v>
+        <v>925</v>
       </c>
       <c r="C47" s="1">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D47" s="1">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1">
+        <v>28</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>11</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>1</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
         <v>5</v>
       </c>
-      <c r="E47" s="1">
-        <v>8</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
-        <v>2</v>
-      </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
       <c r="U47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="1">
         <v>0</v>
@@ -7391,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -7403,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
@@ -7463,31 +7491,31 @@
     </row>
     <row r="48" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="B48" s="1">
-        <v>520</v>
+        <v>859</v>
       </c>
       <c r="C48" s="1">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D48" s="1">
         <v>13</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
@@ -7496,10 +7524,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" s="1">
         <v>3</v>
@@ -7520,19 +7548,19 @@
         <v>0</v>
       </c>
       <c r="T48" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" s="1">
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -7541,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -7604,34 +7632,34 @@
     </row>
     <row r="49" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B49" s="1">
-        <v>492</v>
+        <v>826</v>
       </c>
       <c r="C49" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
       </c>
       <c r="E49" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -7640,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N49" s="1">
         <v>0</v>
@@ -7661,22 +7689,22 @@
         <v>0</v>
       </c>
       <c r="T49" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X49" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
@@ -7745,22 +7773,22 @@
     </row>
     <row r="50" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="B50" s="1">
-        <v>460</v>
+        <v>820</v>
       </c>
       <c r="C50" s="1">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D50" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -7769,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -7781,10 +7809,10 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -7802,10 +7830,10 @@
         <v>0</v>
       </c>
       <c r="T50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U50" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -7817,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="Y50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="1">
         <v>0</v>
@@ -7886,34 +7914,34 @@
     </row>
     <row r="51" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B51" s="1">
-        <v>456</v>
+        <v>817</v>
       </c>
       <c r="C51" s="1">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D51" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F51" s="1">
+        <v>6</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
         <v>2</v>
       </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>4</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
       <c r="J51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
@@ -7922,10 +7950,10 @@
         <v>0</v>
       </c>
       <c r="M51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -7943,10 +7971,10 @@
         <v>0</v>
       </c>
       <c r="T51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U51" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
@@ -8027,88 +8055,88 @@
     </row>
     <row r="52" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>442</v>
+        <v>810</v>
       </c>
       <c r="C52" s="1">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="1">
+      <c r="R52" s="1">
+        <v>1</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1">
+        <v>5</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y52" s="1">
         <v>7</v>
       </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
-        <v>0</v>
-      </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
-      <c r="X52" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
       <c r="Z52" s="1">
         <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="1">
         <v>0</v>
@@ -8168,44 +8196,44 @@
     </row>
     <row r="53" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B53" s="1">
-        <v>418</v>
+        <v>810</v>
       </c>
       <c r="C53" s="1">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D53" s="1">
         <v>13</v>
       </c>
       <c r="E53" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>7</v>
+      </c>
+      <c r="M53" s="1">
         <v>2</v>
       </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1">
-        <v>0</v>
-      </c>
-      <c r="L53" s="1">
-        <v>10</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
       <c r="N53" s="1">
         <v>0</v>
       </c>
@@ -8225,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -8237,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="X53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="1">
         <v>0</v>
@@ -8309,22 +8337,22 @@
     </row>
     <row r="54" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1">
-        <v>394</v>
+        <v>790</v>
       </c>
       <c r="C54" s="1">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D54" s="1">
         <v>13</v>
       </c>
       <c r="E54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -8333,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -8345,10 +8373,10 @@
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N54" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -8357,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -8366,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="T54" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U54" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V54" s="1">
         <v>0</v>
@@ -8450,31 +8478,31 @@
     </row>
     <row r="55" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B55" s="1">
-        <v>385</v>
+        <v>790</v>
       </c>
       <c r="C55" s="1">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F55" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
       </c>
       <c r="I55" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J55" s="1">
         <v>0</v>
@@ -8483,10 +8511,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" s="1">
         <v>0</v>
@@ -8507,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U55" s="1">
         <v>0</v>
@@ -8516,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X55" s="1">
         <v>0</v>
@@ -8591,76 +8619,76 @@
     </row>
     <row r="56" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B56" s="1">
-        <v>364</v>
+        <v>764</v>
       </c>
       <c r="C56" s="1">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D56" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>10</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>5</v>
+      </c>
+      <c r="U56" s="1">
+        <v>1</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="1">
-        <v>8</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
-        <v>5</v>
-      </c>
-      <c r="V56" s="1">
-        <v>0</v>
-      </c>
-      <c r="W56" s="1">
-        <v>0</v>
-      </c>
       <c r="X56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -8669,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="AA56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB56" s="1">
         <v>0</v>
@@ -8732,25 +8760,25 @@
     </row>
     <row r="57" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1">
-        <v>359</v>
+        <v>763</v>
       </c>
       <c r="C57" s="1">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D57" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -8765,40 +8793,40 @@
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="1">
+        <v>5</v>
+      </c>
+      <c r="N57" s="1">
+        <v>4</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>5</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
         <v>1</v>
       </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
       <c r="W57" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
@@ -8873,88 +8901,88 @@
     </row>
     <row r="58" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B58" s="1">
-        <v>358</v>
+        <v>758</v>
       </c>
       <c r="C58" s="1">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D58" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E58" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1">
+        <v>2</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>5</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1">
+        <v>5</v>
+      </c>
+      <c r="U58" s="1">
         <v>1</v>
       </c>
-      <c r="J58" s="1">
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="1">
         <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
-      <c r="T58" s="1">
-        <v>0</v>
-      </c>
-      <c r="U58" s="1">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1">
-        <v>0</v>
-      </c>
-      <c r="W58" s="1">
-        <v>0</v>
-      </c>
-      <c r="X58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>0</v>
       </c>
       <c r="AC58" s="1">
         <v>0</v>
@@ -9014,28 +9042,28 @@
     </row>
     <row r="59" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B59" s="1">
-        <v>350</v>
+        <v>744</v>
       </c>
       <c r="C59" s="1">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F59" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -9047,13 +9075,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -9071,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="T59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V59" s="1">
         <v>0</v>
@@ -9155,106 +9183,106 @@
     </row>
     <row r="60" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B60" s="1">
-        <v>348</v>
+        <v>731</v>
       </c>
       <c r="C60" s="1">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D60" s="1">
         <v>13</v>
       </c>
       <c r="E60" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="1">
+        <v>17</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>7</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="1">
         <v>3</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>2</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1">
-        <v>2</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
-      </c>
-      <c r="V60" s="1">
-        <v>0</v>
-      </c>
-      <c r="W60" s="1">
-        <v>0</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="1">
-        <v>0</v>
       </c>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
@@ -9296,31 +9324,31 @@
     </row>
     <row r="61" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B61" s="1">
-        <v>342</v>
+        <v>671</v>
       </c>
       <c r="C61" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D61" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J61" s="1">
         <v>0</v>
@@ -9329,13 +9357,13 @@
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -9353,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U61" s="1">
         <v>0</v>
@@ -9437,23 +9465,23 @@
     </row>
     <row r="62" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="B62" s="1">
-        <v>307</v>
+        <v>665</v>
       </c>
       <c r="C62" s="1">
+        <v>34</v>
+      </c>
+      <c r="D62" s="1">
+        <v>13</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
         <v>9</v>
       </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="1">
-        <v>2</v>
-      </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
@@ -9461,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1">
         <v>2</v>
@@ -9473,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" s="1">
         <v>2</v>
@@ -9485,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="1">
         <v>0</v>
@@ -9497,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V62" s="1">
         <v>0</v>
@@ -9506,10 +9534,10 @@
         <v>0</v>
       </c>
       <c r="X62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z62" s="1">
         <v>0</v>
@@ -9578,13 +9606,13 @@
     </row>
     <row r="63" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="B63" s="1">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="C63" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D63" s="1">
         <v>13</v>
@@ -9593,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -9608,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -9617,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P63" s="1">
         <v>0</v>
@@ -9635,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U63" s="1">
         <v>0</v>
@@ -9719,22 +9747,22 @@
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B64" s="1">
-        <v>252</v>
+        <v>653</v>
       </c>
       <c r="C64" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
       </c>
       <c r="E64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -9770,28 +9798,28 @@
         <v>0</v>
       </c>
       <c r="R64" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S64" s="1">
         <v>0</v>
       </c>
       <c r="T64" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U64" s="1">
         <v>0</v>
       </c>
       <c r="V64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y64" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z64" s="1">
         <v>0</v>
@@ -9803,7 +9831,7 @@
         <v>0</v>
       </c>
       <c r="AC64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD64" s="1">
         <v>0</v>
@@ -9860,22 +9888,22 @@
     </row>
     <row r="65" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B65" s="1">
-        <v>242</v>
+        <v>652</v>
       </c>
       <c r="C65" s="1">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D65" s="1">
         <v>13</v>
       </c>
       <c r="E65" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -9884,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1">
         <v>0</v>
@@ -9893,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M65" s="1">
         <v>0</v>
@@ -9917,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U65" s="1">
         <v>0</v>
@@ -10001,67 +10029,67 @@
     </row>
     <row r="66" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="B66" s="1">
-        <v>210</v>
+        <v>625</v>
       </c>
       <c r="C66" s="1">
+        <v>39</v>
+      </c>
+      <c r="D66" s="1">
         <v>13</v>
       </c>
-      <c r="D66" s="1">
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
+        <v>15</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>3</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>2</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>1</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
         <v>5</v>
       </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <v>6</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
-      <c r="M66" s="1">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
       <c r="U66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" s="1">
         <v>0</v>
@@ -10070,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -10142,77 +10170,77 @@
     </row>
     <row r="67" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="B67" s="1">
-        <v>210</v>
+        <v>602</v>
       </c>
       <c r="C67" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D67" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="1">
+        <v>10</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>2</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
+        <v>0</v>
+      </c>
+      <c r="X67" s="1">
         <v>4</v>
       </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1">
-        <v>0</v>
-      </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
-      </c>
-      <c r="W67" s="1">
-        <v>0</v>
-      </c>
-      <c r="X67" s="1">
-        <v>0</v>
-      </c>
       <c r="Y67" s="1">
         <v>0</v>
       </c>
@@ -10220,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="AA67" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="1">
         <v>0</v>
@@ -10283,31 +10311,31 @@
     </row>
     <row r="68" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B68" s="1">
-        <v>201</v>
+        <v>580</v>
       </c>
       <c r="C68" s="1">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D68" s="1">
         <v>13</v>
       </c>
       <c r="E68" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I68" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" s="1">
         <v>0</v>
@@ -10319,40 +10347,40 @@
         <v>0</v>
       </c>
       <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
+        <v>5</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>4</v>
+      </c>
+      <c r="X68" s="1">
         <v>1</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -10424,22 +10452,22 @@
     </row>
     <row r="69" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B69" s="1">
-        <v>196</v>
+        <v>580</v>
       </c>
       <c r="C69" s="1">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D69" s="1">
         <v>13</v>
       </c>
       <c r="E69" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F69" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -10448,10 +10476,10 @@
         <v>0</v>
       </c>
       <c r="I69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -10475,13 +10503,13 @@
         <v>0</v>
       </c>
       <c r="R69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S69" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T69" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -10523,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="AH69" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
@@ -10565,22 +10593,22 @@
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="B70" s="1">
-        <v>190</v>
+        <v>558</v>
       </c>
       <c r="C70" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D70" s="1">
         <v>13</v>
       </c>
       <c r="E70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -10601,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N70" s="1">
         <v>0</v>
@@ -10616,13 +10644,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="1">
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -10706,34 +10734,34 @@
     </row>
     <row r="71" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B71" s="1">
-        <v>190</v>
+        <v>542</v>
       </c>
       <c r="C71" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D71" s="1">
         <v>13</v>
       </c>
       <c r="E71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
         <v>3</v>
       </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -10742,7 +10770,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N71" s="1">
         <v>0</v>
@@ -10763,22 +10791,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z71" s="1">
         <v>0</v>
@@ -10847,31 +10875,31 @@
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B72" s="1">
-        <v>180</v>
+        <v>534</v>
       </c>
       <c r="C72" s="1">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D72" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I72" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J72" s="1">
         <v>0</v>
@@ -10880,10 +10908,10 @@
         <v>0</v>
       </c>
       <c r="L72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M72" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N72" s="1">
         <v>0</v>
@@ -10904,16 +10932,16 @@
         <v>0</v>
       </c>
       <c r="T72" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U72" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V72" s="1">
         <v>0</v>
       </c>
       <c r="W72" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
@@ -10925,7 +10953,7 @@
         <v>0</v>
       </c>
       <c r="AA72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB72" s="1">
         <v>0</v>
@@ -10988,22 +11016,22 @@
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B73" s="1">
-        <v>180</v>
+        <v>516</v>
       </c>
       <c r="C73" s="1">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D73" s="1">
         <v>13</v>
       </c>
       <c r="E73" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
@@ -11012,10 +11040,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
@@ -11024,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" s="1">
         <v>0</v>
@@ -11045,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U73" s="1">
         <v>5</v>
@@ -11129,49 +11157,49 @@
     </row>
     <row r="74" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="B74" s="1">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="C74" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D74" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="F74" s="1">
+        <v>2</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>4</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1">
+        <v>2</v>
+      </c>
+      <c r="M74" s="1">
         <v>3</v>
       </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0</v>
-      </c>
-      <c r="I74" s="1">
-        <v>0</v>
-      </c>
-      <c r="J74" s="1">
-        <v>0</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
-      <c r="L74" s="1">
-        <v>0</v>
-      </c>
-      <c r="M74" s="1">
-        <v>0</v>
-      </c>
       <c r="N74" s="1">
         <v>0</v>
       </c>
       <c r="O74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" s="1">
         <v>0</v>
@@ -11189,25 +11217,25 @@
         <v>0</v>
       </c>
       <c r="U74" s="1">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
         <v>1</v>
       </c>
-      <c r="V74" s="1">
-        <v>0</v>
-      </c>
       <c r="W74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z74" s="1">
         <v>0</v>
       </c>
       <c r="AA74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB74" s="1">
         <v>0</v>
@@ -11270,29 +11298,29 @@
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="B75" s="1">
-        <v>160</v>
+        <v>473</v>
       </c>
       <c r="C75" s="1">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F75" s="1">
+        <v>12</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
         <v>3</v>
       </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>0</v>
-      </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
@@ -11303,10 +11331,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" s="1">
         <v>0</v>
@@ -11330,7 +11358,7 @@
         <v>5</v>
       </c>
       <c r="U75" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -11411,22 +11439,22 @@
     </row>
     <row r="76" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B76" s="1">
-        <v>144</v>
+        <v>455</v>
       </c>
       <c r="C76" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E76" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -11450,25 +11478,25 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="O76" s="1">
+        <v>0</v>
+      </c>
+      <c r="P76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
         <v>1</v>
       </c>
-      <c r="O76" s="1">
-        <v>0</v>
-      </c>
-      <c r="P76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="1">
-        <v>0</v>
-      </c>
-      <c r="R76" s="1">
-        <v>0</v>
-      </c>
       <c r="S76" s="1">
         <v>0</v>
       </c>
       <c r="T76" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U76" s="1">
         <v>0</v>
@@ -11552,13 +11580,13 @@
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="B77" s="1">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="C77" s="1">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D77" s="1">
         <v>13</v>
@@ -11600,19 +11628,19 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R77" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S77" s="1">
         <v>0</v>
       </c>
       <c r="T77" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U77" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V77" s="1">
         <v>0</v>
@@ -11693,22 +11721,22 @@
     </row>
     <row r="78" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="B78" s="1">
-        <v>130</v>
+        <v>403</v>
       </c>
       <c r="C78" s="1">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -11717,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -11729,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" s="1">
         <v>0</v>
@@ -11750,16 +11778,16 @@
         <v>0</v>
       </c>
       <c r="T78" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="1">
         <v>0</v>
       </c>
       <c r="W78" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X78" s="1">
         <v>0</v>
@@ -11834,22 +11862,22 @@
     </row>
     <row r="79" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1">
-        <v>110</v>
+        <v>342</v>
       </c>
       <c r="C79" s="1">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D79" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
@@ -11873,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" s="1">
         <v>0</v>
@@ -11906,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="Y79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z79" s="1">
         <v>0</v>
@@ -11975,19 +12003,19 @@
     </row>
     <row r="80" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B80" s="1">
-        <v>86</v>
+        <v>292</v>
       </c>
       <c r="C80" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D80" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E80" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -11999,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -12032,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="T80" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U80" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V80" s="1">
         <v>0</v>
@@ -12116,76 +12144,76 @@
     </row>
     <row r="81" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B81" s="1">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="C81" s="1">
+        <v>16</v>
+      </c>
+      <c r="D81" s="1">
         <v>5</v>
       </c>
-      <c r="D81" s="1">
-        <v>0</v>
-      </c>
       <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>9</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1">
+        <v>0</v>
+      </c>
+      <c r="U81" s="1">
         <v>1</v>
       </c>
-      <c r="F81" s="1">
+      <c r="V81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1">
+        <v>0</v>
+      </c>
+      <c r="X81" s="1">
         <v>1</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>2</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0</v>
-      </c>
-      <c r="L81" s="1">
-        <v>0</v>
-      </c>
-      <c r="M81" s="1">
-        <v>1</v>
-      </c>
-      <c r="N81" s="1">
-        <v>0</v>
-      </c>
-      <c r="O81" s="1">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="1">
-        <v>0</v>
-      </c>
-      <c r="R81" s="1">
-        <v>0</v>
-      </c>
-      <c r="S81" s="1">
-        <v>0</v>
-      </c>
-      <c r="T81" s="1">
-        <v>0</v>
-      </c>
-      <c r="U81" s="1">
-        <v>0</v>
-      </c>
-      <c r="V81" s="1">
-        <v>0</v>
-      </c>
-      <c r="W81" s="1">
-        <v>0</v>
-      </c>
-      <c r="X81" s="1">
-        <v>0</v>
       </c>
       <c r="Y81" s="1">
         <v>0</v>
@@ -12257,73 +12285,73 @@
     </row>
     <row r="82" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B82" s="1">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="C82" s="1">
+        <v>25</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>11</v>
+      </c>
+      <c r="I82" s="1">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1">
+        <v>2</v>
+      </c>
+      <c r="M82" s="1">
+        <v>2</v>
+      </c>
+      <c r="N82" s="1">
+        <v>0</v>
+      </c>
+      <c r="O82" s="1">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>0</v>
+      </c>
+      <c r="S82" s="1">
+        <v>0</v>
+      </c>
+      <c r="T82" s="1">
         <v>5</v>
       </c>
-      <c r="D82" s="1">
-        <v>0</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="1">
-        <v>2</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0</v>
-      </c>
-      <c r="I82" s="1">
-        <v>0</v>
-      </c>
-      <c r="J82" s="1">
-        <v>0</v>
-      </c>
-      <c r="K82" s="1">
-        <v>0</v>
-      </c>
-      <c r="L82" s="1">
-        <v>0</v>
-      </c>
-      <c r="M82" s="1">
-        <v>0</v>
-      </c>
-      <c r="N82" s="1">
-        <v>0</v>
-      </c>
-      <c r="O82" s="1">
-        <v>0</v>
-      </c>
-      <c r="P82" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="1">
-        <v>0</v>
-      </c>
-      <c r="R82" s="1">
-        <v>0</v>
-      </c>
-      <c r="S82" s="1">
-        <v>0</v>
-      </c>
-      <c r="T82" s="1">
-        <v>0</v>
-      </c>
       <c r="U82" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V82" s="1">
         <v>0</v>
       </c>
       <c r="W82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X82" s="1">
         <v>0</v>
@@ -12398,64 +12426,64 @@
     </row>
     <row r="83" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B83" s="1">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="C83" s="1">
+        <v>19</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>6</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1">
+        <v>2</v>
+      </c>
+      <c r="N83" s="1">
+        <v>0</v>
+      </c>
+      <c r="O83" s="1">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1">
+        <v>0</v>
+      </c>
+      <c r="S83" s="1">
+        <v>0</v>
+      </c>
+      <c r="T83" s="1">
         <v>5</v>
-      </c>
-      <c r="D83" s="1">
-        <v>0</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1">
-        <v>0</v>
-      </c>
-      <c r="J83" s="1">
-        <v>0</v>
-      </c>
-      <c r="K83" s="1">
-        <v>0</v>
-      </c>
-      <c r="L83" s="1">
-        <v>0</v>
-      </c>
-      <c r="M83" s="1">
-        <v>0</v>
-      </c>
-      <c r="N83" s="1">
-        <v>0</v>
-      </c>
-      <c r="O83" s="1">
-        <v>0</v>
-      </c>
-      <c r="P83" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="1">
-        <v>0</v>
-      </c>
-      <c r="R83" s="1">
-        <v>0</v>
-      </c>
-      <c r="S83" s="1">
-        <v>0</v>
-      </c>
-      <c r="T83" s="1">
-        <v>0</v>
       </c>
       <c r="U83" s="1">
         <v>5</v>
@@ -12539,65 +12567,65 @@
     </row>
     <row r="84" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B84" s="1">
-        <v>50</v>
+        <v>261</v>
       </c>
       <c r="C84" s="1">
+        <v>22</v>
+      </c>
+      <c r="D84" s="1">
+        <v>13</v>
+      </c>
+      <c r="E84" s="1">
+        <v>3</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>0</v>
+      </c>
+      <c r="O84" s="1">
+        <v>0</v>
+      </c>
+      <c r="P84" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>0</v>
+      </c>
+      <c r="R84" s="1">
+        <v>1</v>
+      </c>
+      <c r="S84" s="1">
+        <v>0</v>
+      </c>
+      <c r="T84" s="1">
         <v>5</v>
       </c>
-      <c r="D84" s="1">
-        <v>5</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0</v>
-      </c>
-      <c r="H84" s="1">
-        <v>0</v>
-      </c>
-      <c r="I84" s="1">
-        <v>0</v>
-      </c>
-      <c r="J84" s="1">
-        <v>0</v>
-      </c>
-      <c r="K84" s="1">
-        <v>0</v>
-      </c>
-      <c r="L84" s="1">
-        <v>0</v>
-      </c>
-      <c r="M84" s="1">
-        <v>0</v>
-      </c>
-      <c r="N84" s="1">
-        <v>0</v>
-      </c>
-      <c r="O84" s="1">
-        <v>0</v>
-      </c>
-      <c r="P84" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="1">
-        <v>0</v>
-      </c>
-      <c r="R84" s="1">
-        <v>0</v>
-      </c>
-      <c r="S84" s="1">
-        <v>0</v>
-      </c>
-      <c r="T84" s="1">
-        <v>0</v>
-      </c>
       <c r="U84" s="1">
         <v>0</v>
       </c>
@@ -12638,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="AH84" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
@@ -12680,67 +12708,67 @@
     </row>
     <row r="85" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B85" s="1">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="C85" s="1">
+        <v>16</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <v>10</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1">
+        <v>0</v>
+      </c>
+      <c r="O85" s="1">
+        <v>0</v>
+      </c>
+      <c r="P85" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>0</v>
+      </c>
+      <c r="R85" s="1">
+        <v>0</v>
+      </c>
+      <c r="S85" s="1">
+        <v>0</v>
+      </c>
+      <c r="T85" s="1">
         <v>5</v>
       </c>
-      <c r="D85" s="1">
-        <v>0</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0</v>
-      </c>
-      <c r="I85" s="1">
-        <v>0</v>
-      </c>
-      <c r="J85" s="1">
-        <v>0</v>
-      </c>
-      <c r="K85" s="1">
-        <v>0</v>
-      </c>
-      <c r="L85" s="1">
-        <v>0</v>
-      </c>
-      <c r="M85" s="1">
-        <v>0</v>
-      </c>
-      <c r="N85" s="1">
-        <v>0</v>
-      </c>
-      <c r="O85" s="1">
-        <v>0</v>
-      </c>
-      <c r="P85" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="1">
-        <v>0</v>
-      </c>
-      <c r="R85" s="1">
-        <v>0</v>
-      </c>
-      <c r="S85" s="1">
-        <v>5</v>
-      </c>
-      <c r="T85" s="1">
-        <v>0</v>
-      </c>
       <c r="U85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85" s="1">
         <v>0</v>
@@ -12821,67 +12849,67 @@
     </row>
     <row r="86" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="B86" s="1">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="C86" s="1">
+        <v>13</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>3</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1">
+        <v>4</v>
+      </c>
+      <c r="N86" s="1">
+        <v>0</v>
+      </c>
+      <c r="O86" s="1">
+        <v>0</v>
+      </c>
+      <c r="P86" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>0</v>
+      </c>
+      <c r="R86" s="1">
+        <v>0</v>
+      </c>
+      <c r="S86" s="1">
+        <v>0</v>
+      </c>
+      <c r="T86" s="1">
         <v>5</v>
       </c>
-      <c r="D86" s="1">
-        <v>0</v>
-      </c>
-      <c r="E86" s="1">
-        <v>0</v>
-      </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1">
-        <v>0</v>
-      </c>
-      <c r="J86" s="1">
-        <v>0</v>
-      </c>
-      <c r="K86" s="1">
-        <v>0</v>
-      </c>
-      <c r="L86" s="1">
-        <v>0</v>
-      </c>
-      <c r="M86" s="1">
-        <v>0</v>
-      </c>
-      <c r="N86" s="1">
-        <v>0</v>
-      </c>
-      <c r="O86" s="1">
-        <v>0</v>
-      </c>
-      <c r="P86" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="1">
-        <v>0</v>
-      </c>
-      <c r="R86" s="1">
-        <v>0</v>
-      </c>
-      <c r="S86" s="1">
-        <v>0</v>
-      </c>
-      <c r="T86" s="1">
-        <v>0</v>
-      </c>
       <c r="U86" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V86" s="1">
         <v>0</v>
@@ -12962,22 +12990,22 @@
     </row>
     <row r="87" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B87" s="1">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="C87" s="1">
+        <v>17</v>
+      </c>
+      <c r="D87" s="1">
+        <v>13</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
         <v>4</v>
-      </c>
-      <c r="D87" s="1">
-        <v>0</v>
-      </c>
-      <c r="E87" s="1">
-        <v>4</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
@@ -13103,76 +13131,76 @@
     </row>
     <row r="88" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="B88" s="1">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C88" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
+      </c>
+      <c r="M88" s="1">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>0</v>
+      </c>
+      <c r="O88" s="1">
+        <v>0</v>
+      </c>
+      <c r="P88" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>0</v>
+      </c>
+      <c r="R88" s="1">
+        <v>0</v>
+      </c>
+      <c r="S88" s="1">
+        <v>0</v>
+      </c>
+      <c r="T88" s="1">
+        <v>5</v>
+      </c>
+      <c r="U88" s="1">
+        <v>0</v>
+      </c>
+      <c r="V88" s="1">
+        <v>0</v>
+      </c>
+      <c r="W88" s="1">
+        <v>0</v>
+      </c>
+      <c r="X88" s="1">
         <v>1</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0</v>
-      </c>
-      <c r="H88" s="1">
-        <v>0</v>
-      </c>
-      <c r="I88" s="1">
-        <v>0</v>
-      </c>
-      <c r="J88" s="1">
-        <v>0</v>
-      </c>
-      <c r="K88" s="1">
-        <v>0</v>
-      </c>
-      <c r="L88" s="1">
-        <v>0</v>
-      </c>
-      <c r="M88" s="1">
-        <v>0</v>
-      </c>
-      <c r="N88" s="1">
-        <v>0</v>
-      </c>
-      <c r="O88" s="1">
-        <v>0</v>
-      </c>
-      <c r="P88" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="1">
-        <v>0</v>
-      </c>
-      <c r="R88" s="1">
-        <v>0</v>
-      </c>
-      <c r="S88" s="1">
-        <v>0</v>
-      </c>
-      <c r="T88" s="1">
-        <v>0</v>
-      </c>
-      <c r="U88" s="1">
-        <v>0</v>
-      </c>
-      <c r="V88" s="1">
-        <v>0</v>
-      </c>
-      <c r="W88" s="1">
-        <v>0</v>
-      </c>
-      <c r="X88" s="1">
-        <v>0</v>
       </c>
       <c r="Y88" s="1">
         <v>0</v>
@@ -13244,13 +13272,13 @@
     </row>
     <row r="89" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B89" s="1">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="C89" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -13259,7 +13287,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
@@ -13301,10 +13329,10 @@
         <v>0</v>
       </c>
       <c r="T89" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U89" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V89" s="1">
         <v>0</v>
@@ -13385,23 +13413,23 @@
     </row>
     <row r="90" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B90" s="1">
+        <v>154</v>
+      </c>
+      <c r="C90" s="1">
         <v>10</v>
       </c>
-      <c r="C90" s="1">
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1">
+        <v>2</v>
+      </c>
+      <c r="F90" s="1">
         <v>1</v>
       </c>
-      <c r="D90" s="1">
-        <v>0</v>
-      </c>
-      <c r="E90" s="1">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
       <c r="G90" s="1">
         <v>0</v>
       </c>
@@ -13442,10 +13470,10 @@
         <v>0</v>
       </c>
       <c r="T90" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" s="1">
         <v>0</v>
@@ -13454,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="X90" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y90" s="1">
         <v>0</v>
@@ -13526,16 +13554,16 @@
     </row>
     <row r="91" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="B91" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C91" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D91" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -13583,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U91" s="1">
         <v>0</v>
@@ -13598,7 +13626,7 @@
         <v>0</v>
       </c>
       <c r="Y91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z91" s="1">
         <v>0</v>
@@ -13667,16 +13695,16 @@
     </row>
     <row r="92" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B92" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -13724,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U92" s="1">
         <v>0</v>
@@ -13807,18 +13835,20 @@
       <c r="BW92" s="1"/>
     </row>
     <row r="93" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
+      <c r="A93" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="B93" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="C93" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -13863,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="T93" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U93" s="1">
         <v>0</v>
@@ -13946,12 +13976,14 @@
       <c r="BW93" s="1"/>
     </row>
     <row r="94" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
+      <c r="A94" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="B94" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C94" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -13993,16 +14025,16 @@
         <v>0</v>
       </c>
       <c r="Q94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" s="1">
         <v>0</v>
       </c>
       <c r="T94" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U94" s="1">
         <v>0</v>
@@ -14085,12 +14117,14 @@
       <c r="BW94" s="1"/>
     </row>
     <row r="95" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
+      <c r="A95" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="B95" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C95" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
@@ -14144,7 +14178,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V95" s="1">
         <v>0</v>
@@ -14224,12 +14258,14 @@
       <c r="BW95" s="1"/>
     </row>
     <row r="96" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
+      <c r="A96" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="B96" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C96" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
@@ -14277,7 +14313,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T96" s="1">
         <v>0</v>
@@ -14363,12 +14399,14 @@
       <c r="BW96" s="1"/>
     </row>
     <row r="97" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
+      <c r="A97" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="B97" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C97" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -14419,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U97" s="1">
         <v>0</v>
@@ -14502,12 +14540,14 @@
       <c r="BW97" s="1"/>
     </row>
     <row r="98" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
+      <c r="A98" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="B98" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C98" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
@@ -14558,7 +14598,7 @@
         <v>0</v>
       </c>
       <c r="T98" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U98" s="1">
         <v>0</v>
@@ -14641,21 +14681,23 @@
       <c r="BW98" s="1"/>
     </row>
     <row r="99" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
+      <c r="A99" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="B99" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C99" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
@@ -14780,21 +14822,108 @@
       <c r="BW99" s="1"/>
     </row>
     <row r="100" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="V100" s="1"/>
-      <c r="W100" s="1"/>
-      <c r="X100" s="1"/>
-      <c r="Y100" s="1"/>
-      <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
-      <c r="AB100" s="1"/>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
-      <c r="AF100" s="1"/>
-      <c r="AG100" s="1"/>
-      <c r="AH100" s="1"/>
+      <c r="A100" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100" s="1">
+        <v>15</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1">
+        <v>0</v>
+      </c>
+      <c r="O100" s="1">
+        <v>0</v>
+      </c>
+      <c r="P100" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>0</v>
+      </c>
+      <c r="R100" s="1">
+        <v>1</v>
+      </c>
+      <c r="S100" s="1">
+        <v>0</v>
+      </c>
+      <c r="T100" s="1">
+        <v>0</v>
+      </c>
+      <c r="U100" s="1">
+        <v>0</v>
+      </c>
+      <c r="V100" s="1">
+        <v>0</v>
+      </c>
+      <c r="W100" s="1">
+        <v>0</v>
+      </c>
+      <c r="X100" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="1">
+        <v>0</v>
+      </c>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
@@ -14833,9 +14962,113 @@
       <c r="BV100" s="1"/>
       <c r="BW100" s="1"/>
     </row>
+    <row r="101" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" s="2">
+        <v>10</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1">
+        <v>0</v>
+      </c>
+      <c r="O101" s="1">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>0</v>
+      </c>
+      <c r="R101" s="1">
+        <v>0</v>
+      </c>
+      <c r="S101" s="1">
+        <v>0</v>
+      </c>
+      <c r="T101" s="1">
+        <v>0</v>
+      </c>
+      <c r="U101" s="1">
+        <v>1</v>
+      </c>
+      <c r="V101" s="2">
+        <v>0</v>
+      </c>
+      <c r="W101" s="2">
+        <v>0</v>
+      </c>
+      <c r="X101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH99">
-    <sortCondition descending="1" ref="B2:B99"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH101">
+    <sortCondition descending="1" ref="B2:B101"/>
   </sortState>
   <conditionalFormatting sqref="A1:BW100">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">

--- a/Results2.xlsx
+++ b/Results2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C3B47C-2FE5-4464-AD4D-0D31F97857BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E304E6-BE78-4F7B-A3BD-19A0A16B5EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2132F57B-8824-4764-BC02-18EC8AEFAB7F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>Name</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Bibiana</t>
   </si>
   <si>
-    <t>Blood Ivy</t>
-  </si>
-  <si>
     <t>BOKIKI</t>
   </si>
   <si>
@@ -148,12 +145,6 @@
   </si>
   <si>
     <t>Calpone</t>
-  </si>
-  <si>
-    <t>charontas</t>
-  </si>
-  <si>
-    <t>Charos</t>
   </si>
   <si>
     <t>Dairon</t>
@@ -273,16 +264,10 @@
     <t>Orod</t>
   </si>
   <si>
-    <t>Pavlare</t>
-  </si>
-  <si>
     <t>R O M E O</t>
   </si>
   <si>
     <t>RAIN</t>
-  </si>
-  <si>
-    <t>raouf</t>
   </si>
   <si>
     <t>Ravenor</t>
@@ -327,12 +312,6 @@
     <t>Tygojas</t>
   </si>
   <si>
-    <t>UBBAtheBronxxx</t>
-  </si>
-  <si>
-    <t>Ulf Vidar</t>
-  </si>
-  <si>
     <t>Valka</t>
   </si>
   <si>
@@ -343,9 +322,6 @@
   </si>
   <si>
     <t>Z sex Machine</t>
-  </si>
-  <si>
-    <t>Zehn</t>
   </si>
   <si>
     <t>Zeus</t>
@@ -428,6 +404,12 @@
   <si>
     <t>Turrosan</t>
   </si>
+  <si>
+    <t>Dario W5</t>
+  </si>
+  <si>
+    <t>skorp</t>
+  </si>
 </sst>
 </file>
 
@@ -477,10 +459,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -915,7 +896,7 @@
         <v>23</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -1005,22 +986,22 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1">
-        <v>6013</v>
+        <v>7241</v>
       </c>
       <c r="C2" s="1">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="D2" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1029,34 +1010,34 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q2" s="1">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="R2" s="1">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -1065,34 +1046,34 @@
         <v>5</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="1">
         <v>0</v>
       </c>
       <c r="Y2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="1">
         <v>0</v>
       </c>
       <c r="AA2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="1">
         <v>0</v>
       </c>
       <c r="AC2" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="1">
         <v>0</v>
@@ -1101,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AG2" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -1146,22 +1127,22 @@
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1">
-        <v>5041</v>
+        <v>6387</v>
       </c>
       <c r="C3" s="1">
-        <v>337</v>
+        <v>201</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1170,70 +1151,70 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N3" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3" s="1">
         <v>0</v>
       </c>
       <c r="Q3" s="1">
-        <v>286</v>
+        <v>1</v>
       </c>
       <c r="R3" s="1">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="S3" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" s="1">
         <v>5</v>
       </c>
       <c r="U3" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="1">
         <v>0</v>
       </c>
       <c r="Y3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="1">
         <v>0</v>
       </c>
       <c r="AA3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD3" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE3" s="1">
         <v>0</v>
@@ -1242,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="AG3" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH3" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
@@ -1287,22 +1268,22 @@
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4" s="1">
-        <v>4567</v>
+        <v>5499</v>
       </c>
       <c r="C4" s="1">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1311,10 +1292,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -1323,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N4" s="1">
         <v>5</v>
@@ -1356,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="Y4" s="1">
         <v>0</v>
@@ -1428,22 +1409,22 @@
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1">
-        <v>4217</v>
+        <v>5204</v>
       </c>
       <c r="C5" s="1">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1458,19 +1439,19 @@
         <v>20</v>
       </c>
       <c r="K5" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L5" s="1">
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" s="1">
         <v>4</v>
       </c>
       <c r="O5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -1482,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T5" s="1">
         <v>5</v>
@@ -1569,19 +1550,19 @@
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1">
-        <v>3812</v>
+        <v>3958</v>
       </c>
       <c r="C6" s="1">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
@@ -1611,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -1710,49 +1691,49 @@
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="B7" s="1">
-        <v>3618</v>
+        <v>3922</v>
       </c>
       <c r="C7" s="1">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -1761,10 +1742,10 @@
         <v>1</v>
       </c>
       <c r="R7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" s="1">
         <v>5</v>
@@ -1776,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X7" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -1788,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="AA7" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB7" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
@@ -1851,31 +1832,31 @@
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1">
-        <v>3542</v>
+        <v>3723</v>
       </c>
       <c r="C8" s="1">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -1884,28 +1865,28 @@
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>6</v>
+      </c>
+      <c r="R8" s="1">
         <v>1</v>
       </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
       <c r="S8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" s="1">
         <v>5</v>
@@ -1917,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -1929,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AA8" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
@@ -1992,13 +1973,13 @@
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B9" s="1">
-        <v>3320</v>
+        <v>3545</v>
       </c>
       <c r="C9" s="1">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
@@ -2007,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2019,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K9" s="1">
         <v>4</v>
@@ -2043,10 +2024,10 @@
         <v>1</v>
       </c>
       <c r="R9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" s="1">
         <v>5</v>
@@ -2133,22 +2114,22 @@
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="B10" s="1">
-        <v>3246</v>
+        <v>3176</v>
       </c>
       <c r="C10" s="1">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2157,25 +2138,25 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>12</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
         <v>20</v>
       </c>
-      <c r="J10" s="1">
-        <v>6</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
       <c r="N10" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O10" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -2211,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB10" s="1">
         <v>0</v>
@@ -2274,49 +2255,49 @@
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B11" s="1">
-        <v>2544</v>
+        <v>3075</v>
       </c>
       <c r="C11" s="1">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I11" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
       <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>27</v>
+      </c>
+      <c r="N11" s="1">
         <v>1</v>
       </c>
-      <c r="M11" s="1">
-        <v>18</v>
-      </c>
-      <c r="N11" s="1">
-        <v>7</v>
-      </c>
       <c r="O11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2328,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" s="1">
         <v>5</v>
@@ -2343,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2352,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -2415,22 +2396,22 @@
     </row>
     <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B12" s="1">
-        <v>2468</v>
+        <v>3020</v>
       </c>
       <c r="C12" s="1">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="D12" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2439,34 +2420,34 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
       </c>
       <c r="Q12" s="1">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="R12" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S12" s="1">
         <v>0</v>
@@ -2487,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2556,58 +2537,58 @@
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1">
-        <v>2450</v>
+        <v>2830</v>
       </c>
       <c r="C13" s="1">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
+        <v>68</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
         <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>17</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>24</v>
-      </c>
-      <c r="N13" s="1">
-        <v>6</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
       </c>
       <c r="S13" s="1">
         <v>0</v>
@@ -2616,31 +2597,31 @@
         <v>5</v>
       </c>
       <c r="U13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>
       </c>
       <c r="W13" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
       </c>
       <c r="Y13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="1">
         <v>0</v>
       </c>
       <c r="AA13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
@@ -2655,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2697,34 +2678,34 @@
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B14" s="1">
-        <v>2435</v>
+        <v>2816</v>
       </c>
       <c r="C14" s="1">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1">
+        <v>35</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
-        <v>34</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>36</v>
-      </c>
-      <c r="I14" s="1">
-        <v>7</v>
-      </c>
       <c r="J14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -2733,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
@@ -2745,13 +2726,13 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T14" s="1">
         <v>5</v>
@@ -2763,19 +2744,19 @@
         <v>0</v>
       </c>
       <c r="W14" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X14" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z14" s="1">
         <v>0</v>
       </c>
       <c r="AA14" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="1">
         <v>0</v>
@@ -2838,61 +2819,61 @@
     </row>
     <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1">
-        <v>2402</v>
+        <v>2790</v>
       </c>
       <c r="C15" s="1">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1">
         <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I15" s="1">
+        <v>4</v>
+      </c>
+      <c r="J15" s="1">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>8</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>4</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
         <v>1</v>
       </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>27</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>5</v>
-      </c>
       <c r="R15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" s="1">
         <v>5</v>
@@ -2904,13 +2885,13 @@
         <v>0</v>
       </c>
       <c r="W15" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="1">
         <v>0</v>
@@ -2937,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2979,22 +2960,22 @@
     </row>
     <row r="16" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1">
-        <v>2395</v>
+        <v>2573</v>
       </c>
       <c r="C16" s="1">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D16" s="1">
         <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -3003,43 +2984,43 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
+        <v>7</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
         <v>3</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>5</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>1</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
       </c>
       <c r="T16" s="1">
         <v>5</v>
       </c>
       <c r="U16" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -3051,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Z16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
@@ -3120,28 +3101,28 @@
     </row>
     <row r="17" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B17" s="1">
-        <v>2301</v>
+        <v>2540</v>
       </c>
       <c r="C17" s="1">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="D17" s="1">
         <v>13</v>
       </c>
       <c r="E17" s="1">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -3156,10 +3137,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -3168,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="1">
         <v>0</v>
       </c>
       <c r="S17" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17" s="1">
         <v>5</v>
@@ -3186,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
@@ -3198,13 +3179,13 @@
         <v>0</v>
       </c>
       <c r="AA17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
       </c>
       <c r="AC17" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -3219,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
@@ -3261,22 +3242,22 @@
     </row>
     <row r="18" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1">
-        <v>2194</v>
+        <v>2442</v>
       </c>
       <c r="C18" s="1">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F18" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -3285,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -3402,22 +3383,22 @@
     </row>
     <row r="19" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B19" s="1">
-        <v>1993</v>
+        <v>2392</v>
       </c>
       <c r="C19" s="1">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
       </c>
       <c r="E19" s="1">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3429,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="J19" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3438,7 +3419,7 @@
         <v>41</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
@@ -3453,10 +3434,10 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T19" s="1">
         <v>5</v>
@@ -3543,22 +3524,22 @@
     </row>
     <row r="20" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B20" s="1">
-        <v>1970</v>
+        <v>2346</v>
       </c>
       <c r="C20" s="1">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -3579,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N20" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -3591,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
         <v>0</v>
@@ -3615,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="1">
         <v>0</v>
@@ -3630,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3684,22 +3665,22 @@
     </row>
     <row r="21" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B21" s="1">
-        <v>1933</v>
+        <v>2338</v>
       </c>
       <c r="C21" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -3708,37 +3689,37 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1">
+        <v>10</v>
+      </c>
+      <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>5</v>
+      </c>
+      <c r="O21" s="1">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
         <v>3</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>17</v>
-      </c>
-      <c r="N21" s="1">
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
         <v>3</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
       </c>
       <c r="T21" s="1">
         <v>5</v>
@@ -3753,26 +3734,26 @@
         <v>0</v>
       </c>
       <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD21" s="1">
         <v>3</v>
       </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1">
-        <v>19</v>
-      </c>
-      <c r="AB21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>0</v>
-      </c>
       <c r="AE21" s="1">
         <v>0</v>
       </c>
@@ -3780,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="AG21" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH21" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3825,22 +3806,22 @@
     </row>
     <row r="22" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1">
-        <v>1880</v>
+        <v>2225</v>
       </c>
       <c r="C22" s="1">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -3852,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -3867,19 +3848,19 @@
         <v>0</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P22" s="1">
         <v>0</v>
       </c>
       <c r="Q22" s="1">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="R22" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T22" s="1">
         <v>5</v>
@@ -3897,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="Y22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22" s="1">
         <v>0</v>
@@ -3924,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3966,47 +3947,47 @@
     </row>
     <row r="23" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1">
-        <v>1845</v>
+        <v>2190</v>
       </c>
       <c r="C23" s="1">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>20</v>
+      </c>
+      <c r="J23" s="1">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
         <v>18</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>3</v>
-      </c>
-      <c r="I23" s="1">
-        <v>4</v>
-      </c>
-      <c r="J23" s="1">
-        <v>5</v>
-      </c>
-      <c r="K23" s="1">
-        <v>11</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>4</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
       <c r="O23" s="1">
         <v>0</v>
       </c>
@@ -4017,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
         <v>0</v>
@@ -4065,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="AH23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -4107,46 +4088,46 @@
     </row>
     <row r="24" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="B24" s="1">
-        <v>1818</v>
+        <v>2095</v>
       </c>
       <c r="C24" s="1">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E24" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J24" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -4167,7 +4148,7 @@
         <v>5</v>
       </c>
       <c r="U24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -4176,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -4188,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" s="1">
         <v>0</v>
@@ -4248,22 +4229,22 @@
     </row>
     <row r="25" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B25" s="1">
-        <v>1789</v>
+        <v>2034</v>
       </c>
       <c r="C25" s="1">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D25" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -4272,11 +4253,11 @@
         <v>0</v>
       </c>
       <c r="I25" s="1">
+        <v>7</v>
+      </c>
+      <c r="J25" s="1">
         <v>3</v>
       </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
       <c r="K25" s="1">
         <v>0</v>
       </c>
@@ -4284,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -4302,22 +4283,22 @@
         <v>0</v>
       </c>
       <c r="S25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" s="1">
         <v>5</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
       </c>
       <c r="W25" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -4326,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -4389,37 +4370,37 @@
     </row>
     <row r="26" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B26" s="1">
-        <v>1785</v>
+        <v>2018</v>
       </c>
       <c r="C26" s="1">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J26" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K26" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -4428,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
@@ -4440,10 +4421,10 @@
         <v>1</v>
       </c>
       <c r="R26" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T26" s="1">
         <v>5</v>
@@ -4458,22 +4439,22 @@
         <v>0</v>
       </c>
       <c r="X26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="1">
         <v>3</v>
-      </c>
-      <c r="Z26" s="1">
-        <v>7</v>
-      </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -4530,13 +4511,13 @@
     </row>
     <row r="27" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1">
-        <v>1675</v>
+        <v>2000</v>
       </c>
       <c r="C27" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
@@ -4545,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -4554,37 +4535,37 @@
         <v>0</v>
       </c>
       <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>13</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
         <v>5</v>
       </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>2</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>4</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <v>1</v>
       </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
       <c r="S27" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" s="1">
         <v>5</v>
@@ -4599,25 +4580,25 @@
         <v>0</v>
       </c>
       <c r="X27" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z27" s="1">
         <v>0</v>
       </c>
       <c r="AA27" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="1">
         <v>0</v>
       </c>
       <c r="AD27" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE27" s="1">
         <v>0</v>
@@ -4629,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
@@ -4671,22 +4652,22 @@
     </row>
     <row r="28" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B28" s="1">
-        <v>1660</v>
+        <v>1990</v>
       </c>
       <c r="C28" s="1">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F28" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -4695,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="1">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J28" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4707,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N28" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -4719,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -4731,28 +4712,28 @@
         <v>5</v>
       </c>
       <c r="U28" s="1">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
         <v>2</v>
       </c>
-      <c r="V28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="1">
-        <v>0</v>
-      </c>
       <c r="X28" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="1">
         <v>0</v>
       </c>
       <c r="AA28" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="1">
         <v>0</v>
@@ -4812,22 +4793,22 @@
     </row>
     <row r="29" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1">
-        <v>1630</v>
+        <v>1891</v>
       </c>
       <c r="C29" s="1">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D29" s="1">
         <v>13</v>
       </c>
       <c r="E29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -4836,13 +4817,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J29" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -4851,16 +4832,16 @@
         <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" s="1">
         <v>0</v>
       </c>
       <c r="Q29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
@@ -4872,7 +4853,7 @@
         <v>5</v>
       </c>
       <c r="U29" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -4884,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="1">
         <v>0</v>
@@ -4893,10 +4874,10 @@
         <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
@@ -4908,10 +4889,10 @@
         <v>0</v>
       </c>
       <c r="AG29" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
@@ -4953,22 +4934,22 @@
     </row>
     <row r="30" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B30" s="1">
-        <v>1490</v>
+        <v>1869</v>
       </c>
       <c r="C30" s="1">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D30" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4977,10 +4958,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J30" s="1">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4992,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -5001,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
@@ -5013,7 +4994,7 @@
         <v>5</v>
       </c>
       <c r="U30" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -5025,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="1">
         <v>0</v>
@@ -5094,22 +5075,22 @@
     </row>
     <row r="31" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1">
-        <v>1461</v>
+        <v>1748</v>
       </c>
       <c r="C31" s="1">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -5121,7 +5102,7 @@
         <v>5</v>
       </c>
       <c r="J31" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -5130,10 +5111,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N31" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -5235,46 +5216,46 @@
     </row>
     <row r="32" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
-        <v>1434</v>
+        <v>1726</v>
       </c>
       <c r="C32" s="1">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1">
+        <v>72</v>
+      </c>
+      <c r="F32" s="1">
+        <v>5</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="1">
-        <v>33</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>10</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
       <c r="L32" s="1">
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -5289,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32" s="1">
         <v>5</v>
@@ -5301,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="1">
         <v>0</v>
@@ -5376,46 +5357,46 @@
     </row>
     <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="B33" s="1">
-        <v>1426</v>
+        <v>1675</v>
       </c>
       <c r="C33" s="1">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>11</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
         <v>5</v>
       </c>
-      <c r="E33" s="1">
-        <v>8</v>
-      </c>
-      <c r="F33" s="1">
-        <v>7</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
       <c r="J33" s="1">
         <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N33" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -5424,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -5445,19 +5426,19 @@
         <v>0</v>
       </c>
       <c r="X33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y33" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z33" s="1">
         <v>0</v>
       </c>
       <c r="AA33" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" s="1">
         <v>0</v>
@@ -5475,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -5517,58 +5498,58 @@
     </row>
     <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B34" s="1">
-        <v>1370</v>
+        <v>1617</v>
       </c>
       <c r="C34" s="1">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E34" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" s="1">
+        <v>9</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
         <v>4</v>
       </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>19</v>
-      </c>
-      <c r="J34" s="1">
-        <v>8</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
       <c r="N34" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
       </c>
       <c r="Q34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="1">
         <v>0</v>
@@ -5586,19 +5567,19 @@
         <v>0</v>
       </c>
       <c r="X34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
       <c r="AB34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -5658,22 +5639,22 @@
     </row>
     <row r="35" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1">
-        <v>1369</v>
+        <v>1615</v>
       </c>
       <c r="C35" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D35" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E35" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -5685,34 +5666,34 @@
         <v>0</v>
       </c>
       <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
         <v>8</v>
       </c>
-      <c r="K35" s="1">
-        <v>2</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
       <c r="M35" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N35" s="1">
+        <v>6</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>3</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
       <c r="S35" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>5</v>
@@ -5721,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
@@ -5730,19 +5711,19 @@
         <v>0</v>
       </c>
       <c r="Y35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
       </c>
       <c r="AA35" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
       <c r="AC35" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="1">
         <v>0</v>
@@ -5799,28 +5780,28 @@
     </row>
     <row r="36" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1">
-        <v>1349</v>
+        <v>1571</v>
       </c>
       <c r="C36" s="1">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D36" s="1">
         <v>13</v>
       </c>
       <c r="E36" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -5832,13 +5813,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -5847,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -5859,25 +5840,25 @@
         <v>5</v>
       </c>
       <c r="U36" s="1">
+        <v>0</v>
+      </c>
+      <c r="V36" s="1">
+        <v>2</v>
+      </c>
+      <c r="W36" s="1">
         <v>3</v>
       </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
-      <c r="W36" s="1">
-        <v>0</v>
-      </c>
       <c r="X36" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y36" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
       </c>
       <c r="AA36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" s="1">
         <v>1</v>
@@ -5940,13 +5921,13 @@
     </row>
     <row r="37" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1">
-        <v>1265</v>
+        <v>1565</v>
       </c>
       <c r="C37" s="1">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
@@ -6012,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="Y37" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z37" s="1">
         <v>0</v>
@@ -6081,47 +6062,47 @@
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B38" s="1">
-        <v>1254</v>
+        <v>1545</v>
       </c>
       <c r="C38" s="1">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F38" s="1">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>10</v>
+      </c>
+      <c r="K38" s="1">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
         <v>5</v>
       </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="N38" s="1">
         <v>1</v>
       </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>10</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
       <c r="O38" s="1">
         <v>0</v>
       </c>
@@ -6129,13 +6110,13 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
       </c>
       <c r="S38" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T38" s="1">
         <v>5</v>
@@ -6147,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" s="1">
         <v>0</v>
@@ -6159,13 +6140,13 @@
         <v>0</v>
       </c>
       <c r="AA38" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
       <c r="AC38" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
@@ -6222,22 +6203,22 @@
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1">
-        <v>1235</v>
+        <v>1490</v>
       </c>
       <c r="C39" s="1">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -6246,10 +6227,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -6261,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -6270,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
@@ -6294,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="Y39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
@@ -6363,22 +6344,22 @@
     </row>
     <row r="40" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B40" s="1">
-        <v>1220</v>
+        <v>1469</v>
       </c>
       <c r="C40" s="1">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F40" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -6387,19 +6368,19 @@
         <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J40" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1">
         <v>0</v>
@@ -6423,7 +6404,7 @@
         <v>5</v>
       </c>
       <c r="U40" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -6432,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y40" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z40" s="1">
         <v>0</v>
@@ -6444,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC40" s="1">
         <v>0</v>
@@ -6504,22 +6485,22 @@
     </row>
     <row r="41" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B41" s="1">
-        <v>1204</v>
+        <v>1449</v>
       </c>
       <c r="C41" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D41" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
@@ -6531,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -6540,10 +6521,10 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -6552,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" s="1">
         <v>0</v>
@@ -6645,61 +6626,61 @@
     </row>
     <row r="42" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1">
-        <v>1177</v>
+        <v>1436</v>
       </c>
       <c r="C42" s="1">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1">
+        <v>13</v>
+      </c>
+      <c r="F42" s="1">
+        <v>6</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>6</v>
+      </c>
+      <c r="J42" s="1">
+        <v>7</v>
+      </c>
+      <c r="K42" s="1">
+        <v>2</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>5</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="1">
-        <v>22</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>28</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-      <c r="N42" s="1">
-        <v>1</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
       <c r="R42" s="1">
         <v>0</v>
       </c>
       <c r="S42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" s="1">
         <v>5</v>
@@ -6714,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="1">
         <v>0</v>
@@ -6786,22 +6767,22 @@
     </row>
     <row r="43" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B43" s="1">
-        <v>1170</v>
+        <v>1387</v>
       </c>
       <c r="C43" s="1">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="D43" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F43" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -6810,34 +6791,34 @@
         <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N43" s="1">
         <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1">
         <v>0</v>
       </c>
       <c r="Q43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" s="1">
         <v>0</v>
@@ -6852,22 +6833,22 @@
         <v>0</v>
       </c>
       <c r="W43" s="1">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="X43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="1">
         <v>0</v>
       </c>
       <c r="AB43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="1">
         <v>0</v>
@@ -6927,31 +6908,31 @@
     </row>
     <row r="44" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="B44" s="1">
-        <v>1078</v>
+        <v>1358</v>
       </c>
       <c r="C44" s="1">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1">
+        <v>8</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
         <v>13</v>
       </c>
-      <c r="E44" s="1">
-        <v>39</v>
-      </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
       <c r="I44" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J44" s="1">
         <v>0</v>
@@ -6960,13 +6941,13 @@
         <v>0</v>
       </c>
       <c r="L44" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M44" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -6975,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -6990,16 +6971,16 @@
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z44" s="1">
         <v>0</v>
@@ -7068,55 +7049,55 @@
     </row>
     <row r="45" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1">
-        <v>951</v>
+        <v>1344</v>
       </c>
       <c r="C45" s="1">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="D45" s="1">
         <v>13</v>
       </c>
       <c r="E45" s="1">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
         <v>2</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>0</v>
       </c>
       <c r="R45" s="1">
         <v>0</v>
@@ -7134,13 +7115,13 @@
         <v>0</v>
       </c>
       <c r="W45" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="1">
         <v>0</v>
@@ -7209,19 +7190,19 @@
     </row>
     <row r="46" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B46" s="1">
-        <v>943</v>
+        <v>1305</v>
       </c>
       <c r="C46" s="1">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -7233,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J46" s="1">
         <v>0</v>
@@ -7245,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N46" s="1">
         <v>0</v>
@@ -7257,10 +7238,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="1">
         <v>0</v>
@@ -7278,19 +7259,19 @@
         <v>0</v>
       </c>
       <c r="X46" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y46" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
       <c r="AB46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="1">
         <v>0</v>
@@ -7350,22 +7331,22 @@
     </row>
     <row r="47" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B47" s="1">
-        <v>925</v>
+        <v>1300</v>
       </c>
       <c r="C47" s="1">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -7374,22 +7355,22 @@
         <v>0</v>
       </c>
       <c r="I47" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -7398,13 +7379,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
       </c>
       <c r="S47" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T47" s="1">
         <v>5</v>
@@ -7419,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -7428,10 +7409,10 @@
         <v>0</v>
       </c>
       <c r="AA47" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
@@ -7491,46 +7472,46 @@
     </row>
     <row r="48" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="B48" s="1">
-        <v>859</v>
+        <v>1287</v>
       </c>
       <c r="C48" s="1">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D48" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F48" s="1">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
+        <v>28</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
         <v>1</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1">
-        <v>2</v>
       </c>
       <c r="M48" s="1">
         <v>3</v>
       </c>
       <c r="N48" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -7554,13 +7535,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W48" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -7569,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -7632,32 +7613,32 @@
     </row>
     <row r="49" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B49" s="1">
-        <v>826</v>
+        <v>1274</v>
       </c>
       <c r="C49" s="1">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
       </c>
       <c r="E49" s="1">
+        <v>12</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
         <v>13</v>
       </c>
-      <c r="F49" s="1">
-        <v>7</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
       <c r="J49" s="1">
         <v>0</v>
       </c>
@@ -7668,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N49" s="1">
         <v>0</v>
@@ -7686,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T49" s="1">
         <v>5</v>
@@ -7707,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="Z49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
       <c r="AB49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" s="1">
         <v>0</v>
@@ -7731,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="AH49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
@@ -7773,31 +7754,31 @@
     </row>
     <row r="50" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="B50" s="1">
-        <v>820</v>
+        <v>1251</v>
       </c>
       <c r="C50" s="1">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F50" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I50" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
@@ -7809,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N50" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -7827,22 +7808,22 @@
         <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T50" s="1">
         <v>5</v>
       </c>
       <c r="U50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -7851,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="AA50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
@@ -7914,55 +7895,55 @@
     </row>
     <row r="51" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B51" s="1">
-        <v>817</v>
+        <v>1235</v>
       </c>
       <c r="C51" s="1">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1">
+        <v>25</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>15</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>4</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1">
         <v>1</v>
-      </c>
-      <c r="F51" s="1">
-        <v>6</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
-        <v>2</v>
-      </c>
-      <c r="J51" s="1">
-        <v>5</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>1</v>
-      </c>
-      <c r="N51" s="1">
-        <v>6</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
@@ -7974,7 +7955,7 @@
         <v>5</v>
       </c>
       <c r="U51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
@@ -8055,85 +8036,85 @@
     </row>
     <row r="52" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1">
-        <v>810</v>
+        <v>1190</v>
       </c>
       <c r="C52" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>7</v>
+      </c>
+      <c r="J52" s="1">
         <v>13</v>
       </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
       <c r="K52" s="1">
         <v>0</v>
       </c>
       <c r="L52" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N52" s="1">
         <v>0</v>
       </c>
       <c r="O52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
       </c>
       <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
         <v>1</v>
       </c>
-      <c r="R52" s="1">
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1">
-        <v>5</v>
-      </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
-        <v>0</v>
-      </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
-      <c r="X52" s="1">
-        <v>6</v>
-      </c>
-      <c r="Y52" s="1">
-        <v>7</v>
-      </c>
       <c r="Z52" s="1">
         <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -8196,22 +8177,22 @@
     </row>
     <row r="53" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="B53" s="1">
-        <v>810</v>
+        <v>1146</v>
       </c>
       <c r="C53" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D53" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
@@ -8220,25 +8201,25 @@
         <v>0</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="1">
         <v>0</v>
@@ -8247,13 +8228,13 @@
         <v>0</v>
       </c>
       <c r="R53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="1">
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -8265,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="X53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="1">
         <v>0</v>
@@ -8337,13 +8318,13 @@
     </row>
     <row r="54" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B54" s="1">
-        <v>790</v>
+        <v>1145</v>
       </c>
       <c r="C54" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D54" s="1">
         <v>13</v>
@@ -8352,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -8364,34 +8345,34 @@
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N54" s="1">
+        <v>8</v>
+      </c>
+      <c r="O54" s="1">
+        <v>2</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>1</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
         <v>3</v>
-      </c>
-      <c r="O54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>6</v>
-      </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-      <c r="S54" s="1">
-        <v>0</v>
       </c>
       <c r="T54" s="1">
         <v>5</v>
@@ -8478,61 +8459,61 @@
     </row>
     <row r="55" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B55" s="1">
-        <v>790</v>
+        <v>1075</v>
       </c>
       <c r="C55" s="1">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D55" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E55" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>5</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
         <v>3</v>
       </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
         <v>3</v>
-      </c>
-      <c r="M55" s="1">
-        <v>2</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
       </c>
       <c r="T55" s="1">
         <v>5</v>
@@ -8550,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="Y55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55" s="1">
         <v>0</v>
@@ -8562,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="AC55" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD55" s="1">
         <v>0</v>
@@ -8577,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="AH55" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
@@ -8619,22 +8600,22 @@
     </row>
     <row r="56" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="B56" s="1">
-        <v>764</v>
+        <v>1050</v>
       </c>
       <c r="C56" s="1">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D56" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -8643,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J56" s="1">
         <v>0</v>
@@ -8667,10 +8648,10 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="1">
         <v>0</v>
@@ -8679,16 +8660,16 @@
         <v>5</v>
       </c>
       <c r="U56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="1">
         <v>0</v>
       </c>
       <c r="W56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -8697,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="AA56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB56" s="1">
         <v>0</v>
@@ -8760,22 +8741,22 @@
     </row>
     <row r="57" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="B57" s="1">
-        <v>763</v>
+        <v>975</v>
       </c>
       <c r="C57" s="1">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F57" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
@@ -8784,37 +8765,37 @@
         <v>0</v>
       </c>
       <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>7</v>
+      </c>
+      <c r="M57" s="1">
+        <v>2</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
         <v>1</v>
       </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>5</v>
-      </c>
-      <c r="N57" s="1">
-        <v>4</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
       <c r="R57" s="1">
         <v>0</v>
       </c>
       <c r="S57" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T57" s="1">
         <v>5</v>
@@ -8823,13 +8804,13 @@
         <v>0</v>
       </c>
       <c r="V57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y57" s="1">
         <v>0</v>
@@ -8901,46 +8882,46 @@
     </row>
     <row r="58" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B58" s="1">
-        <v>758</v>
+        <v>951</v>
       </c>
       <c r="C58" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D58" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E58" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1">
+        <v>3</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>3</v>
+      </c>
+      <c r="N58" s="1">
         <v>2</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>3</v>
-      </c>
-      <c r="I58" s="1">
-        <v>2</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <v>5</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
       </c>
       <c r="O58" s="1">
         <v>0</v>
@@ -8961,19 +8942,19 @@
         <v>5</v>
       </c>
       <c r="U58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
+        <v>2</v>
+      </c>
+      <c r="X58" s="1">
         <v>1</v>
       </c>
-      <c r="V58" s="1">
-        <v>0</v>
-      </c>
-      <c r="W58" s="1">
-        <v>0</v>
-      </c>
-      <c r="X58" s="1">
-        <v>8</v>
-      </c>
       <c r="Y58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z58" s="1">
         <v>0</v>
@@ -8982,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="1">
         <v>0</v>
@@ -9042,31 +9023,31 @@
     </row>
     <row r="59" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B59" s="1">
-        <v>744</v>
+        <v>951</v>
       </c>
       <c r="C59" s="1">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F59" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="1">
         <v>0</v>
@@ -9075,13 +9056,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -9102,13 +9083,13 @@
         <v>5</v>
       </c>
       <c r="U59" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V59" s="1">
         <v>0</v>
       </c>
       <c r="W59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
@@ -9183,85 +9164,85 @@
     </row>
     <row r="60" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="B60" s="1">
-        <v>731</v>
+        <v>920</v>
       </c>
       <c r="C60" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D60" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E60" s="1">
+        <v>6</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>2</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>12</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
         <v>3</v>
       </c>
-      <c r="F60" s="1">
-        <v>17</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>7</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
       <c r="T60" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
       </c>
       <c r="W60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="1">
         <v>0</v>
       </c>
       <c r="AA60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB60" s="1">
         <v>0</v>
@@ -9282,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="AH60" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
@@ -9324,31 +9305,31 @@
     </row>
     <row r="61" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="B61" s="1">
-        <v>671</v>
+        <v>919</v>
       </c>
       <c r="C61" s="1">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I61" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J61" s="1">
         <v>0</v>
@@ -9357,13 +9338,13 @@
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M61" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -9465,67 +9446,67 @@
     </row>
     <row r="62" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B62" s="1">
-        <v>665</v>
+        <v>866</v>
       </c>
       <c r="C62" s="1">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D62" s="1">
         <v>13</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F62" s="1">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
         <v>2</v>
       </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0</v>
-      </c>
-      <c r="M62" s="1">
-        <v>0</v>
-      </c>
-      <c r="N62" s="1">
-        <v>2</v>
-      </c>
-      <c r="O62" s="1">
-        <v>0</v>
-      </c>
-      <c r="P62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>1</v>
-      </c>
-      <c r="R62" s="1">
-        <v>0</v>
-      </c>
       <c r="S62" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T62" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U62" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V62" s="1">
         <v>0</v>
@@ -9534,10 +9515,10 @@
         <v>0</v>
       </c>
       <c r="X62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="1">
         <v>0</v>
@@ -9606,22 +9587,22 @@
     </row>
     <row r="63" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="B63" s="1">
-        <v>660</v>
+        <v>839</v>
       </c>
       <c r="C63" s="1">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D63" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F63" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -9636,19 +9617,19 @@
         <v>0</v>
       </c>
       <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
         <v>1</v>
       </c>
-      <c r="L63" s="1">
-        <v>0</v>
-      </c>
       <c r="M63" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N63" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P63" s="1">
         <v>0</v>
@@ -9666,10 +9647,10 @@
         <v>5</v>
       </c>
       <c r="U63" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="1">
         <v>0</v>
@@ -9747,13 +9728,13 @@
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B64" s="1">
-        <v>653</v>
+        <v>835</v>
       </c>
       <c r="C64" s="1">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
@@ -9762,13 +9743,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -9783,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64" s="1">
         <v>0</v>
@@ -9795,13 +9776,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T64" s="1">
         <v>5</v>
@@ -9816,10 +9797,10 @@
         <v>0</v>
       </c>
       <c r="X64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="1">
         <v>0</v>
@@ -9831,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="AC64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD64" s="1">
         <v>0</v>
@@ -9888,22 +9869,22 @@
     </row>
     <row r="65" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="B65" s="1">
-        <v>652</v>
+        <v>832</v>
       </c>
       <c r="C65" s="1">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D65" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F65" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -9912,22 +9893,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O65" s="1">
         <v>0</v>
@@ -9936,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -10029,22 +10010,22 @@
     </row>
     <row r="66" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="B66" s="1">
-        <v>625</v>
+        <v>831</v>
       </c>
       <c r="C66" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D66" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F66" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -10053,37 +10034,37 @@
         <v>0</v>
       </c>
       <c r="I66" s="1">
+        <v>6</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>5</v>
+      </c>
+      <c r="N66" s="1">
+        <v>2</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
         <v>3</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
-      <c r="M66" s="1">
-        <v>2</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>1</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
       </c>
       <c r="T66" s="1">
         <v>5</v>
@@ -10110,7 +10091,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="1">
         <v>0</v>
@@ -10170,76 +10151,76 @@
     </row>
     <row r="67" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B67" s="1">
-        <v>602</v>
+        <v>830</v>
       </c>
       <c r="C67" s="1">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2</v>
+      </c>
+      <c r="I67" s="1">
+        <v>10</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>2</v>
+      </c>
+      <c r="M67" s="1">
+        <v>14</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>3</v>
+      </c>
+      <c r="T67" s="1">
+        <v>5</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="1">
-        <v>10</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1">
-        <v>2</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>1</v>
-      </c>
-      <c r="M67" s="1">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1">
-        <v>1</v>
-      </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
-      </c>
-      <c r="W67" s="1">
-        <v>0</v>
-      </c>
       <c r="X67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y67" s="1">
         <v>0</v>
@@ -10248,10 +10229,10 @@
         <v>0</v>
       </c>
       <c r="AA67" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" s="1">
         <v>0</v>
@@ -10311,76 +10292,76 @@
     </row>
     <row r="68" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="B68" s="1">
-        <v>580</v>
+        <v>796</v>
       </c>
       <c r="C68" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D68" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1">
+        <v>18</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
         <v>4</v>
       </c>
-      <c r="G68" s="1">
+      <c r="I68" s="1">
         <v>1</v>
       </c>
-      <c r="H68" s="1">
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>6</v>
+      </c>
+      <c r="M68" s="1">
+        <v>2</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
         <v>5</v>
       </c>
-      <c r="I68" s="1">
-        <v>2</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
       <c r="U68" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V68" s="1">
         <v>0</v>
       </c>
       <c r="W68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -10452,19 +10433,19 @@
     </row>
     <row r="69" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B69" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
       <c r="C69" s="1">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D69" s="1">
         <v>13</v>
       </c>
       <c r="E69" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F69" s="1">
         <v>9</v>
@@ -10473,25 +10454,25 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
         <v>2</v>
       </c>
-      <c r="J69" s="1">
-        <v>1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-      <c r="L69" s="1">
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <v>0</v>
-      </c>
       <c r="N69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" s="1">
         <v>0</v>
@@ -10503,16 +10484,16 @@
         <v>0</v>
       </c>
       <c r="R69" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S69" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T69" s="1">
         <v>5</v>
       </c>
       <c r="U69" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V69" s="1">
         <v>0</v>
@@ -10593,22 +10574,22 @@
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B70" s="1">
-        <v>558</v>
+        <v>755</v>
       </c>
       <c r="C70" s="1">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D70" s="1">
         <v>13</v>
       </c>
       <c r="E70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -10620,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -10629,10 +10610,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" s="1">
         <v>0</v>
@@ -10641,20 +10622,20 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1">
         <v>1</v>
       </c>
-      <c r="S70" s="1">
-        <v>0</v>
-      </c>
-      <c r="T70" s="1">
+      <c r="U70" s="1">
         <v>5</v>
       </c>
-      <c r="U70" s="1">
-        <v>0</v>
-      </c>
       <c r="V70" s="1">
         <v>0</v>
       </c>
@@ -10662,10 +10643,10 @@
         <v>0</v>
       </c>
       <c r="X70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" s="1">
         <v>0</v>
@@ -10734,13 +10715,13 @@
     </row>
     <row r="71" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B71" s="1">
-        <v>542</v>
+        <v>705</v>
       </c>
       <c r="C71" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D71" s="1">
         <v>13</v>
@@ -10758,7 +10739,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="1">
         <v>1</v>
@@ -10767,10 +10748,10 @@
         <v>0</v>
       </c>
       <c r="L71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N71" s="1">
         <v>0</v>
@@ -10788,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T71" s="1">
         <v>5</v>
@@ -10800,10 +10781,10 @@
         <v>1</v>
       </c>
       <c r="W71" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="1">
         <v>1</v>
@@ -10875,28 +10856,28 @@
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="B72" s="1">
-        <v>534</v>
+        <v>700</v>
       </c>
       <c r="C72" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E72" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F72" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I72" s="1">
         <v>3</v>
@@ -10908,7 +10889,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" s="1">
         <v>2</v>
@@ -10923,10 +10904,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" s="1">
         <v>0</v>
@@ -10941,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
@@ -10953,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="AA72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB72" s="1">
         <v>0</v>
@@ -11016,43 +10997,43 @@
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="B73" s="1">
-        <v>516</v>
+        <v>656</v>
       </c>
       <c r="C73" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
         <v>13</v>
       </c>
-      <c r="E73" s="1">
-        <v>3</v>
-      </c>
       <c r="F73" s="1">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>7</v>
+      </c>
+      <c r="I73" s="1">
         <v>4</v>
       </c>
-      <c r="G73" s="1">
-        <v>0</v>
-      </c>
-      <c r="H73" s="1">
-        <v>0</v>
-      </c>
-      <c r="I73" s="1">
-        <v>1</v>
-      </c>
       <c r="J73" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
       </c>
       <c r="L73" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M73" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N73" s="1">
         <v>0</v>
@@ -11076,13 +11057,13 @@
         <v>5</v>
       </c>
       <c r="U73" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V73" s="1">
         <v>0</v>
       </c>
       <c r="W73" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X73" s="1">
         <v>0</v>
@@ -11094,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="AA73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB73" s="1">
         <v>0</v>
@@ -11157,49 +11138,49 @@
     </row>
     <row r="74" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="B74" s="1">
-        <v>491</v>
+        <v>646</v>
       </c>
       <c r="C74" s="1">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E74" s="1">
+        <v>9</v>
+      </c>
+      <c r="F74" s="1">
+        <v>6</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="1">
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1">
         <v>2</v>
       </c>
-      <c r="G74" s="1">
-        <v>0</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0</v>
-      </c>
-      <c r="I74" s="1">
-        <v>4</v>
-      </c>
-      <c r="J74" s="1">
-        <v>0</v>
-      </c>
       <c r="K74" s="1">
         <v>0</v>
       </c>
       <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
         <v>2</v>
       </c>
-      <c r="M74" s="1">
-        <v>3</v>
-      </c>
       <c r="N74" s="1">
         <v>0</v>
       </c>
       <c r="O74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="1">
         <v>0</v>
@@ -11214,13 +11195,13 @@
         <v>0</v>
       </c>
       <c r="T74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W74" s="1">
         <v>0</v>
@@ -11229,13 +11210,13 @@
         <v>0</v>
       </c>
       <c r="Y74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="1">
         <v>0</v>
       </c>
       <c r="AA74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB74" s="1">
         <v>0</v>
@@ -11298,28 +11279,28 @@
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="B75" s="1">
-        <v>473</v>
+        <v>588</v>
       </c>
       <c r="C75" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D75" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E75" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
@@ -11331,25 +11312,25 @@
         <v>0</v>
       </c>
       <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>9</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1">
         <v>2</v>
       </c>
-      <c r="M75" s="1">
+      <c r="R75" s="1">
         <v>1</v>
-      </c>
-      <c r="N75" s="1">
-        <v>0</v>
-      </c>
-      <c r="O75" s="1">
-        <v>0</v>
-      </c>
-      <c r="P75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>0</v>
-      </c>
-      <c r="R75" s="1">
-        <v>0</v>
       </c>
       <c r="S75" s="1">
         <v>0</v>
@@ -11439,22 +11420,22 @@
     </row>
     <row r="76" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="B76" s="1">
-        <v>455</v>
+        <v>569</v>
       </c>
       <c r="C76" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D76" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -11463,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J76" s="1">
         <v>0</v>
@@ -11475,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="M76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76" s="1">
         <v>0</v>
@@ -11490,10 +11471,10 @@
         <v>0</v>
       </c>
       <c r="R76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T76" s="1">
         <v>5</v>
@@ -11508,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y76" s="1">
         <v>0</v>
@@ -11580,13 +11561,13 @@
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B77" s="1">
-        <v>440</v>
+        <v>560</v>
       </c>
       <c r="C77" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D77" s="1">
         <v>13</v>
@@ -11595,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -11628,19 +11609,19 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R77" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S77" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T77" s="1">
         <v>5</v>
       </c>
       <c r="U77" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V77" s="1">
         <v>0</v>
@@ -11721,19 +11702,19 @@
     </row>
     <row r="78" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B78" s="1">
-        <v>403</v>
+        <v>540</v>
       </c>
       <c r="C78" s="1">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -11745,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -11757,25 +11738,25 @@
         <v>0</v>
       </c>
       <c r="M78" s="1">
+        <v>9</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>1</v>
+      </c>
+      <c r="R78" s="1">
+        <v>2</v>
+      </c>
+      <c r="S78" s="1">
         <v>3</v>
-      </c>
-      <c r="N78" s="1">
-        <v>0</v>
-      </c>
-      <c r="O78" s="1">
-        <v>0</v>
-      </c>
-      <c r="P78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="1">
-        <v>0</v>
-      </c>
-      <c r="R78" s="1">
-        <v>0</v>
-      </c>
-      <c r="S78" s="1">
-        <v>0</v>
       </c>
       <c r="T78" s="1">
         <v>5</v>
@@ -11787,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X78" s="1">
         <v>0</v>
@@ -11862,67 +11843,67 @@
     </row>
     <row r="79" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>342</v>
+        <v>485</v>
       </c>
       <c r="C79" s="1">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D79" s="1">
         <v>13</v>
       </c>
       <c r="E79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1">
         <v>7</v>
       </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0</v>
-      </c>
-      <c r="J79" s="1">
-        <v>0</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" s="1">
-        <v>0</v>
-      </c>
-      <c r="M79" s="1">
-        <v>0</v>
-      </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="1">
-        <v>0</v>
-      </c>
       <c r="R79" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S79" s="1">
         <v>0</v>
       </c>
       <c r="T79" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U79" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V79" s="1">
         <v>0</v>
@@ -11946,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="AC79" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD79" s="1">
         <v>0</v>
@@ -12003,31 +11984,31 @@
     </row>
     <row r="80" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B80" s="1">
-        <v>292</v>
+        <v>475</v>
       </c>
       <c r="C80" s="1">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
         <v>13</v>
       </c>
-      <c r="E80" s="1">
-        <v>6</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0</v>
-      </c>
       <c r="I80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -12036,10 +12017,10 @@
         <v>0</v>
       </c>
       <c r="L80" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N80" s="1">
         <v>0</v>
@@ -12069,10 +12050,10 @@
         <v>0</v>
       </c>
       <c r="W80" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80" s="1">
         <v>0</v>
@@ -12144,67 +12125,67 @@
     </row>
     <row r="81" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="B81" s="1">
-        <v>270</v>
+        <v>459</v>
       </c>
       <c r="C81" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>1</v>
+      </c>
+      <c r="N81" s="1">
+        <v>2</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1">
         <v>5</v>
       </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="1">
-        <v>9</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0</v>
-      </c>
-      <c r="L81" s="1">
-        <v>0</v>
-      </c>
-      <c r="M81" s="1">
-        <v>0</v>
-      </c>
-      <c r="N81" s="1">
-        <v>0</v>
-      </c>
-      <c r="O81" s="1">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="1">
-        <v>0</v>
-      </c>
-      <c r="R81" s="1">
-        <v>0</v>
-      </c>
-      <c r="S81" s="1">
-        <v>0</v>
-      </c>
-      <c r="T81" s="1">
-        <v>0</v>
-      </c>
       <c r="U81" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="1">
         <v>0</v>
@@ -12285,28 +12266,28 @@
     </row>
     <row r="82" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B82" s="1">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="C82" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
@@ -12318,10 +12299,10 @@
         <v>0</v>
       </c>
       <c r="L82" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N82" s="1">
         <v>0</v>
@@ -12345,16 +12326,16 @@
         <v>5</v>
       </c>
       <c r="U82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="1">
         <v>0</v>
       </c>
       <c r="W82" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="1">
         <v>0</v>
@@ -12426,22 +12407,22 @@
     </row>
     <row r="83" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B83" s="1">
-        <v>262</v>
+        <v>348</v>
       </c>
       <c r="C83" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
@@ -12459,10 +12440,10 @@
         <v>0</v>
       </c>
       <c r="L83" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N83" s="1">
         <v>0</v>
@@ -12480,13 +12461,13 @@
         <v>0</v>
       </c>
       <c r="S83" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T83" s="1">
         <v>5</v>
       </c>
       <c r="U83" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V83" s="1">
         <v>0</v>
@@ -12567,10 +12548,10 @@
     </row>
     <row r="84" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B84" s="1">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="C84" s="1">
         <v>22</v>
@@ -12579,10 +12560,10 @@
         <v>13</v>
       </c>
       <c r="E84" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F84" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G84" s="1">
         <v>0</v>
@@ -12606,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" s="1">
         <v>0</v>
@@ -12618,13 +12599,13 @@
         <v>0</v>
       </c>
       <c r="R84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" s="1">
         <v>0</v>
       </c>
       <c r="T84" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U84" s="1">
         <v>0</v>
@@ -12666,7 +12647,7 @@
         <v>0</v>
       </c>
       <c r="AH84" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
@@ -12708,13 +12689,13 @@
     </row>
     <row r="85" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B85" s="1">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="C85" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -12723,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
@@ -12849,19 +12830,19 @@
     </row>
     <row r="86" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B86" s="1">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C86" s="1">
+        <v>26</v>
+      </c>
+      <c r="D86" s="1">
         <v>13</v>
       </c>
-      <c r="D86" s="1">
-        <v>0</v>
-      </c>
       <c r="E86" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -12873,7 +12854,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="1">
         <v>0</v>
@@ -12885,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N86" s="1">
         <v>0</v>
@@ -12990,22 +12971,22 @@
     </row>
     <row r="87" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B87" s="1">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="C87" s="1">
         <v>17</v>
       </c>
       <c r="D87" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
@@ -13026,7 +13007,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" s="1">
         <v>0</v>
@@ -13047,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U87" s="1">
         <v>0</v>
@@ -13131,19 +13112,19 @@
     </row>
     <row r="88" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B88" s="1">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -13155,7 +13136,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J88" s="1">
         <v>0</v>
@@ -13200,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="X88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="1">
         <v>0</v>
@@ -13272,7 +13253,7 @@
     </row>
     <row r="89" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B89" s="1">
         <v>160</v>
@@ -13413,19 +13394,19 @@
     </row>
     <row r="90" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B90" s="1">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C90" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D90" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -13461,7 +13442,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="1">
         <v>0</v>
@@ -13482,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="X90" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="1">
         <v>0</v>
@@ -13554,65 +13535,65 @@
     </row>
     <row r="91" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B91" s="1">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C91" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D91" s="1">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>0</v>
+      </c>
+      <c r="O91" s="1">
+        <v>0</v>
+      </c>
+      <c r="P91" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>1</v>
+      </c>
+      <c r="R91" s="1">
+        <v>2</v>
+      </c>
+      <c r="S91" s="1">
+        <v>3</v>
+      </c>
+      <c r="T91" s="1">
         <v>5</v>
       </c>
-      <c r="E91" s="1">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0</v>
-      </c>
-      <c r="H91" s="1">
-        <v>0</v>
-      </c>
-      <c r="I91" s="1">
-        <v>0</v>
-      </c>
-      <c r="J91" s="1">
-        <v>0</v>
-      </c>
-      <c r="K91" s="1">
-        <v>0</v>
-      </c>
-      <c r="L91" s="1">
-        <v>0</v>
-      </c>
-      <c r="M91" s="1">
-        <v>0</v>
-      </c>
-      <c r="N91" s="1">
-        <v>0</v>
-      </c>
-      <c r="O91" s="1">
-        <v>0</v>
-      </c>
-      <c r="P91" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="1">
-        <v>0</v>
-      </c>
-      <c r="R91" s="1">
-        <v>0</v>
-      </c>
-      <c r="S91" s="1">
-        <v>0</v>
-      </c>
-      <c r="T91" s="1">
-        <v>2</v>
-      </c>
       <c r="U91" s="1">
         <v>0</v>
       </c>
@@ -13626,7 +13607,7 @@
         <v>0</v>
       </c>
       <c r="Y91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="1">
         <v>0</v>
@@ -13695,64 +13676,64 @@
     </row>
     <row r="92" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="B92" s="1">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C92" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>0</v>
+      </c>
+      <c r="O92" s="1">
+        <v>0</v>
+      </c>
+      <c r="P92" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>1</v>
+      </c>
+      <c r="R92" s="1">
+        <v>0</v>
+      </c>
+      <c r="S92" s="1">
         <v>5</v>
       </c>
-      <c r="E92" s="1">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1">
-        <v>0</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1">
-        <v>0</v>
-      </c>
-      <c r="I92" s="1">
-        <v>0</v>
-      </c>
-      <c r="J92" s="1">
-        <v>0</v>
-      </c>
-      <c r="K92" s="1">
-        <v>0</v>
-      </c>
-      <c r="L92" s="1">
-        <v>0</v>
-      </c>
-      <c r="M92" s="1">
-        <v>0</v>
-      </c>
-      <c r="N92" s="1">
-        <v>0</v>
-      </c>
-      <c r="O92" s="1">
-        <v>0</v>
-      </c>
-      <c r="P92" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="1">
-        <v>0</v>
-      </c>
-      <c r="R92" s="1">
-        <v>0</v>
-      </c>
-      <c r="S92" s="1">
-        <v>0</v>
-      </c>
       <c r="T92" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U92" s="1">
         <v>0</v>
@@ -13836,19 +13817,19 @@
     </row>
     <row r="93" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" s="1">
         <v>50</v>
       </c>
-      <c r="B93" s="1">
-        <v>88</v>
-      </c>
       <c r="C93" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -13890,10 +13871,10 @@
         <v>0</v>
       </c>
       <c r="S93" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T93" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U93" s="1">
         <v>0</v>
@@ -13977,13 +13958,13 @@
     </row>
     <row r="94" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B94" s="1">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C94" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
@@ -14025,19 +14006,19 @@
         <v>0</v>
       </c>
       <c r="Q94" s="1">
+        <v>0</v>
+      </c>
+      <c r="R94" s="1">
+        <v>0</v>
+      </c>
+      <c r="S94" s="1">
+        <v>0</v>
+      </c>
+      <c r="T94" s="1">
+        <v>0</v>
+      </c>
+      <c r="U94" s="1">
         <v>1</v>
-      </c>
-      <c r="R94" s="1">
-        <v>1</v>
-      </c>
-      <c r="S94" s="1">
-        <v>0</v>
-      </c>
-      <c r="T94" s="1">
-        <v>5</v>
-      </c>
-      <c r="U94" s="1">
-        <v>0</v>
       </c>
       <c r="V94" s="1">
         <v>0</v>
@@ -14118,13 +14099,13 @@
     </row>
     <row r="95" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="B95" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C95" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
@@ -14178,7 +14159,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V95" s="1">
         <v>0</v>
@@ -14258,14 +14239,12 @@
       <c r="BW95" s="1"/>
     </row>
     <row r="96" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C96" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
@@ -14313,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T96" s="1">
         <v>0</v>
@@ -14399,14 +14378,12 @@
       <c r="BW96" s="1"/>
     </row>
     <row r="97" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C97" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
@@ -14457,7 +14434,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U97" s="1">
         <v>0</v>
@@ -14540,14 +14517,12 @@
       <c r="BW97" s="1"/>
     </row>
     <row r="98" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C98" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
@@ -14598,7 +14573,7 @@
         <v>0</v>
       </c>
       <c r="T98" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U98" s="1">
         <v>0</v>
@@ -14681,23 +14656,21 @@
       <c r="BW98" s="1"/>
     </row>
     <row r="99" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C99" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
@@ -14822,14 +14795,12 @@
       <c r="BW99" s="1"/>
     </row>
     <row r="100" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>117</v>
-      </c>
+      <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -14874,7 +14845,7 @@
         <v>0</v>
       </c>
       <c r="R100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" s="1">
         <v>0</v>
@@ -14963,19 +14934,16 @@
       <c r="BW100" s="1"/>
     </row>
     <row r="101" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B101" s="2">
-        <v>10</v>
+      <c r="B101">
+        <v>0</v>
       </c>
       <c r="C101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101">
         <v>0</v>
       </c>
       <c r="F101" s="1">
@@ -15024,45 +14992,45 @@
         <v>0</v>
       </c>
       <c r="U101" s="1">
-        <v>1</v>
-      </c>
-      <c r="V101" s="2">
-        <v>0</v>
-      </c>
-      <c r="W101" s="2">
-        <v>0</v>
-      </c>
-      <c r="X101" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="2">
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0</v>
+      </c>
+      <c r="X101">
+        <v>0</v>
+      </c>
+      <c r="Y101">
+        <v>0</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
+      </c>
+      <c r="AA101">
+        <v>0</v>
+      </c>
+      <c r="AB101">
         <v>0</v>
       </c>
       <c r="AC101" s="1">
         <v>0</v>
       </c>
-      <c r="AD101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG101" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="2">
+      <c r="AD101">
+        <v>0</v>
+      </c>
+      <c r="AE101">
+        <v>0</v>
+      </c>
+      <c r="AF101">
+        <v>0</v>
+      </c>
+      <c r="AG101">
+        <v>0</v>
+      </c>
+      <c r="AH101">
         <v>0</v>
       </c>
     </row>
@@ -15078,7 +15046,7 @@
   <conditionalFormatting sqref="B1:B100">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
       <formula>1</formula>
-      <formula>2499</formula>
+      <formula>1399</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:BW100">
